--- a/singscore_new_code/results/Deep_search_results/deepsearch_2_CORRECTED_data_prompt1_results_pathway_name_curated.csv.xlsx
+++ b/singscore_new_code/results/Deep_search_results/deepsearch_2_CORRECTED_data_prompt1_results_pathway_name_curated.csv.xlsx
@@ -8,19 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GS\PySingscore_replicate\singscore_new_code\results\Deep_search_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1ADF0EF-0D6E-4533-926D-11A69B80B9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A1C588-4F1D-4319-A039-065EBDF2CE56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2CB371E1-5584-44EB-81C2-385450FA2A4A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="7" xr2:uid="{2CB371E1-5584-44EB-81C2-385450FA2A4A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Paclitaxel_corrected" sheetId="1" r:id="rId1"/>
-    <sheet name="Anastrazole_corrected" sheetId="2" r:id="rId2"/>
-    <sheet name="Fulvestrant_corrected" sheetId="3" r:id="rId3"/>
-    <sheet name="Palbociclib_corrected" sheetId="4" r:id="rId4"/>
-    <sheet name="Alpelisib_corrected" sheetId="5" r:id="rId5"/>
+    <sheet name="Alpelisib_corrected" sheetId="5" r:id="rId1"/>
+    <sheet name="Abemaciclib_corrected" sheetId="6" r:id="rId2"/>
+    <sheet name="Anastrozole_corrected" sheetId="2" r:id="rId3"/>
+    <sheet name="Atezolizumab_corrected" sheetId="8" r:id="rId4"/>
+    <sheet name="Bevacizumab_corrected" sheetId="9" r:id="rId5"/>
+    <sheet name="Capivasertib_corrected" sheetId="10" r:id="rId6"/>
+    <sheet name="Dostarlimab_corrected" sheetId="11" r:id="rId7"/>
+    <sheet name="Elacestrant_corrected" sheetId="12" r:id="rId8"/>
+    <sheet name="Fulvestrant_corrected" sheetId="3" r:id="rId9"/>
+    <sheet name="Palbociclib_corrected" sheetId="4" r:id="rId10"/>
+    <sheet name="Paclitaxel_corrected" sheetId="1" r:id="rId11"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Paclitaxel_corrected!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Paclitaxel_corrected!$A$1:$F$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="477">
   <si>
     <t>Pathway</t>
   </si>
@@ -814,13 +821,2240 @@
   </si>
   <si>
     <t>HALLMARK_MTORC1_SIGNALING</t>
+  </si>
+  <si>
+    <t>Pathway (ID/Name)</t>
+  </si>
+  <si>
+    <t>Regulation (corrected)</t>
+  </si>
+  <si>
+    <t>Effect (corrected)</t>
+  </si>
+  <si>
+    <t>Rationale (correct, baseline-focused)</t>
+  </si>
+  <si>
+    <t>References (short labels)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> at baseline (high proliferation, high G1–S throughput)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Sensitive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (requires functional RB1)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Abemaciclib selectively inhibits CDK4/6, blocking RB phosphorylation and G1–S progression in RB-proficient cells. HR⁺/HER2– tumors with high proliferative indices (e.g. high Ki-67, strong cell-cycle signatures) are more dependent on CDK4/6-RB signaling and derive greater benefit; effective treatment drives </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>on-treatment downregulation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of G1–S genes.</t>
+    </r>
+  </si>
+  <si>
+    <t>MONARCH 1 &amp; 3 (abemaciclib efficacy, HR⁺/HER2–)(PMC); Mechanistic reviews of CDK4/6i–RB axis(ScienceDirect)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> at baseline (RB1-controlled E2F activity)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Sensitive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (if RB1 intact; excessive RB-independent E2F can drive resistance)</t>
+    </r>
+  </si>
+  <si>
+    <t>In RB1-proficient tumors, CDK4/6-mediated RB phosphorylation releases E2F, inducing DNA replication genes (polymerases, MCMs, CDC6, etc.). Abemaciclib blocks RB phosphorylation, re-pressing E2F targets. Moderate to high E2F-target expression reflecting active but RB-dependent cycling tends to mark tumors that respond; extreme E2F activation via RB loss/c-MYC can bypass CDK4/6 and confer resistance.</t>
+  </si>
+  <si>
+    <t>E2F–RB–CDK4/6 mechanistic reviews(ScienceDirect)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> at baseline in luminal HR⁺ tumors</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Sensitive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (luminal ER-dependent disease)</t>
+    </r>
+  </si>
+  <si>
+    <t>ER signaling induces CCND1 (cyclin D1) and promotes CDK4/6 activity. Luminal ER⁺/HER2– tumors with intact ER signaling and dependence on estrogen-driven cyclin D1 show the greatest benefit from ET + CDK4/6i; ET plus abemaciclib suppresses ER target genes and cell cycle. Loss of ER or an “ER-low/non-luminal” phenotype associates with poorer CDK4/6i benefit.</t>
+  </si>
+  <si>
+    <t>CDK4/6i in ER⁺/HER2– BC and ET combinations(tbcr.amegroups.org)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> at baseline</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Sensitive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (dependency on CDK4/6)</t>
+    </r>
+  </si>
+  <si>
+    <t>Overexpression/amplification of cyclin D1 (CCND1) or high CDK4/6 levels mark tumors that rely on this axis for RB phosphorylation and G1–S entry. Such tumors are particularly vulnerable to abemaciclib; pharmacologic CDK4/6 inhibition reduces pRb and arrests cells in G1.</t>
+  </si>
+  <si>
+    <t>CDK4/6 pathway dependence and sensitivity markers(PMC)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> at baseline (CCNE1 amplification/overexpression, high CDK2)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Resistant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (bypass)</t>
+    </r>
+  </si>
+  <si>
+    <t>Cyclin E–CDK2 can maintain RB phosphorylation and drive S-phase entry even when CDK4/6 is inhibited. Clinical and translational data show high CCNE1 expression associates with short PFS and resistance to palbociclib/abemaciclib; low CCNE1 correlates with better outcomes.</t>
+  </si>
+  <si>
+    <t>Mechanisms of CDK4/6i resistance via cyclin E–CDK2(PMC)</t>
+  </si>
+  <si>
+    <t>RB1 is the canonical target of CDK4/6i. Tumors with RB1 loss-of-function (genomic loss, truncating mutation, complete protein loss) fail to undergo G1 arrest with CDK4/6 blockade and are essentially insensitive to abemaciclib. RB1 loss is a well-described mechanism of both de novo and acquired CDK4/6i resistance.</t>
+  </si>
+  <si>
+    <t>RB1 loss and CDK4/6i resistance(Annals of Oncology)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> at baseline (PIK3CA/PTEN/AKT/mTOR alterations, pathway hyperactivation)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Resistant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (partial; promotes survival &amp; endocrine resistance)</t>
+    </r>
+  </si>
+  <si>
+    <t>Activation of PI3K/AKT/mTOR supports cell growth and survival independent of cyclin D–CDK4/6, and is enriched in endocrine-resistant tumors. Functional proteomic and resistance-model studies show PI3K/AKT/mTOR upregulation in CDK4/6i-resistant breast cancer; dual CDK4/6 + PI3K/mTOR targeting can restore apoptosis and overcome resistance.</t>
+  </si>
+  <si>
+    <t>PI3K/AKT/mTOR &amp; CDK4/6i resistance and combinations(PMC)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> at baseline (FGFR1 amplification/overexpression, FGF ligands, MAPK activation)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Resistant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (alternative growth driver)</t>
+    </r>
+  </si>
+  <si>
+    <t>FGFR1 amplification and MAPK activation induce cyclins and CDK6, providing an alternative proliferative drive that bypasses CDK4/6 blockade. In ER⁺ breast cancer, FGFR1-altered models and patients show resistance to ET + CDK4/6i, which can be mitigated by FGFR inhibitors.</t>
+  </si>
+  <si>
+    <t>FGFR1 amplification and CDK4/6i resistance(PubMed)</t>
+  </si>
+  <si>
+    <r>
+      <t>High p16 in RB-disrupted context</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Resistant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Low/absent p16 with intact RB1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → often </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sensitive</t>
+    </r>
+  </si>
+  <si>
+    <t>Context-dependent; high p16 usually flags resistance</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CDKN2A/p16^INK4A^ normally inhibits cyclin D–CDK4/6. In many HR⁺ breast cancers, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>loss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of p16 is part of the oncogenic program and may mark CDK4/6 dependence and sensitivity; conversely, high p16 frequently accompanies RB1 dysfunction or other cell-cycle rewiring, correlating with poor response to CDK4/6i in several datasets and xenograft models. Thus “p16 up” is generally a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>red flag</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for resistance when it reflects an abnormal RB loop.</t>
+    </r>
+  </si>
+  <si>
+    <t>p16/CDKN2A &amp; CDK4/6i response (reviews and translational data)(SpringerLink)</t>
+  </si>
+  <si>
+    <r>
+      <t>Upregulation is primarily post-treatment/adaptive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (CDK4/6i-induced PD-L1 on tumor and immune cells)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Acquired/adaptive resistance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to monotherapy; potential target for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>combination</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with PD-1/PD-L1 blockade</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CDK4/6 inhibition (including abemaciclib) modulates the tumor immune microenvironment, increasing antigen presentation and T-cell infiltration but also inducing PD-L1 upregulation as a negative feedback. This PD-L1 increase is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>treatment-associated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, not a classic baseline selection marker; it may limit long-term responses unless combined with immune checkpoint blockade.</t>
+    </r>
+  </si>
+  <si>
+    <t>CDK4/6i-induced PD-L1 and synergy with ICB(ScienceDirect)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>after</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CDK4/6i (therapy-induced senescence and SASP)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dual</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – can support </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sensitivity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> via immune recruitment in “hot” tumors, but may promote </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>resistance/progression</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in “cold” or chronically treated settings</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Abemaciclib and other CDK4/6i induce a therapy-induced senescence (TIS) program with a SASP comprising IL-6, IL-8, interferons and chemokines. In immune-competent settings, this can enhance antitumor immunity and deepen responses; however, chronic SASP can also foster tumor growth, EMT, and resistance. Thus SASP upregulation is mainly an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>on-treatment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> feature rather than a baseline predictor, with context-dependent effects.</t>
+    </r>
+  </si>
+  <si>
+    <t>CDK4/6i-induced senescence &amp; SASP(PMC)</t>
+  </si>
+  <si>
+    <t>Down / lost FAT1–Hippo signaling at baseline</t>
+  </si>
+  <si>
+    <t>Loss of FAT1 impairs Hippo tumor-suppressor signaling, leading to nuclear YAP/TAZ accumulation and transcriptional upregulation of CDK6 and other proliferative genes. Functional genomics screens and clinical correlates in ER⁺ breast cancer show FAT1 and other Hippo alterations as recurrent drivers of CDK4/6i resistance.</t>
+  </si>
+  <si>
+    <t>FAT1–Hippo alterations and CDK4/6i resistance(PMC)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> at baseline (high proliferation); </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>on-treatment fall</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = response</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Sensitive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if TK1 drops markedly after starting abemaciclib; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>resistant/poor prognosis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if TK1 remains high or rises</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TK1 activity reflects S-phase flux and is downstream of CDK4/6–RB–E2F signaling. Patients starting CDK4/6i + ET with high baseline TK1 but showing a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>robust early decline</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in TK1 activity have better PFS; persistent or rising TK1 on therapy marks early progression. Thus TK1 is best viewed as a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pharmacodynamic marker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, with baseline high proliferation compatible with sensitivity but on-treatment decrease being the key favorable sign.</t>
+    </r>
+  </si>
+  <si>
+    <t>TK1 as a pharmacodynamic biomarker for CDK4/6i(PMC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation (summarized) </t>
+  </si>
+  <si>
+    <t>effect (summarized)</t>
+  </si>
+  <si>
+    <t>Senstitive</t>
+  </si>
+  <si>
+    <t>KEGG_CELL_CYCLE</t>
+  </si>
+  <si>
+    <t>HALLMARK_ESTROGEN_RESPONSE_EARLY</t>
+  </si>
+  <si>
+    <t>REACTOME_CYCLIN_E_ASSOCIATED_EVENTS_DURING_G1_S_TRANSITION</t>
+  </si>
+  <si>
+    <t>REACTOME_CYCLIN_D_ASSOCIATED_EVENTS_IN_G1</t>
+  </si>
+  <si>
+    <t>REACTOME_SIGNALING_BY_FGFR1</t>
+  </si>
+  <si>
+    <r>
+      <t>Down / lost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> at baseline (RB1 mutation/deletion, loss of expression)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Resistant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (intrinsic or acquired)</t>
+    </r>
+  </si>
+  <si>
+    <t>REACTOME_ABERRANT_REGULATION_OF_MITOTIC_G_S_TRANSITION_IN_CANCER_DUE_TO_RB1_DEFECTS</t>
+  </si>
+  <si>
+    <t>KEGG_MEDICUS_REFERENCE_P16_CELL_CYCLE_G1_S</t>
+  </si>
+  <si>
+    <t>KEGG_MEDICUS_REFERENCE_PDL_PD1_SHP_PI3K_SIGNALING_PATHWAY</t>
+  </si>
+  <si>
+    <t>HALLMARK_INFLAMMATORY_RESPONSE</t>
+  </si>
+  <si>
+    <t>REACTOME_SIGNALING_BY_HIPPO</t>
+  </si>
+  <si>
+    <t>Rationale (correct)</t>
+  </si>
+  <si>
+    <t>References (corrected)</t>
+  </si>
+  <si>
+    <t>A high IFN-γ gene signature at baseline reflects a pre-existing antitumor immune response with increased MHC expression, chemokines and PD-L1 induction. Across tumors and in TNBC neoadjuvant/biomarker work, IFN-γ–related mRNA profiles predict better response to PD-1/PD-L1 blockade, including atezolizumab-containing regimens. (PMC)</t>
+  </si>
+  <si>
+    <t>Ayers et al., J Clin Invest 2017 (IFN-γ mRNA profile &amp; PD-1 response, PMID 28729376).(PMC) Li et al., Front Med 2022 (IFN-γ-related signatures &amp; TNBC).(Frontiers) Dugo et al., Clin Cancer Res 2024 – DetermaIO predicts pCR with neoadjuvant atezo+chemo in TNBC.(PMC)</t>
+  </si>
+  <si>
+    <t>The “allograft rejection” set captures cytotoxic CD8⁺ T-cell/NK infiltration and Th1-type inflammation. Such T-cell-inflamed signatures correlate with higher response rates to PD-1/PD-L1 inhibitors and are incorporated into immune-related gene signatures predicting atezo benefit in TNBC. (AACR Journals)</t>
+  </si>
+  <si>
+    <t>Emens et al., IMpassion130 biomarker analyses – inflamed TME and atezo benefit in PD-L1+ mTNBC.(PMC) Dugo et al., Clin Cancer Res 2024 – immune-related 27-gene signature (including T-cell activation) predicts response to neoadjuvant atezolizumab.(PMC)</t>
+  </si>
+  <si>
+    <t>Up (PD-L1 present)</t>
+  </si>
+  <si>
+    <t>Baseline activation of the PD-1/PD-L1 axis (especially PD-L1 expression on tumor-infiltrating immune cells) provides the pharmacologic target for atezolizumab. In IMpassion130, clinical benefit was restricted to PD-L1+ mTNBC, supporting that an “on” PD-1/PD-L1 pathway predicts sensitivity. (New England Journal of Medicine)</t>
+  </si>
+  <si>
+    <t>Schmid et al., N Engl J Med 2018 – IMpassion130 atezo+nab-paclitaxel in mTNBC, PD-L1-dependent benefit.(New England Journal of Medicine) Rugo et al., J Natl Cancer Inst 2021 – PD-L1 IHC assay and atezo benefit in TNBC.(OUP Academic) Jin et al., 2024 breast PD-1/PD-L1 review.(PMC)</t>
+  </si>
+  <si>
+    <t>Tumor-intrinsic Wnt/β-catenin activation is linked to non-T-cell-inflamed, immune-excluded tumors with loss of dendritic-cell recruitment and poor CD8⁺ infiltration, leading to primary resistance to ICIs. Although much data are from melanoma and other cancers, this immune-excluded program is relevant to breast TNBC. (Frontiers)</t>
+  </si>
+  <si>
+    <t>Li et al., Front Immunol 2019 – Wnt/β-catenin drives T-cell exclusion.(Frontiers) Chehrazi-Raffle et al., Cancers 2021 – Wnt/β-catenin and ICI resistance.(MDPI) Trujillo et al., JITC 2019 – β-catenin activation and secondary ICI resistance.(Journal of Investigative Medicine)</t>
+  </si>
+  <si>
+    <t>High TGF-β and EMT signatures define an immune-excluded phenotype with dense stroma and peritumoral T-cell trapping. In atezolizumab-treated urothelial cancer and in TNBC biomarker studies, stromal TGF-β signaling is associated with poor response, while TGF-β blockade plus anti-PD-L1 restores intratumoral CD8⁺ T-cell infiltration and antitumor activity. (PMC)</t>
+  </si>
+  <si>
+    <t>Mariathasan et al., Nature 2018 – stromal TGF-β signature → resistance to atezolizumab in “excluded” tumors.(PMC) Casadevall et al., JCO Precis Oncol 2019 – TGF-β activation and PD-L1 resistance in TNBC case.(ASCO Publications) Yi et al., J Immunother Cancer 2022 – anti-TGF-β/PD-L1 bispecific improves TNBC control.(Journal of Investigative Medicine)</t>
+  </si>
+  <si>
+    <t>Downregulation or loss of antigen processing/presentation (e.g., B2M, HLA-I, TAP defects, or JAK/IFN signaling mutations) prevents CD8⁺ T cells from recognizing tumor cells, causing primary or acquired resistance to PD-1/PD-L1 blockade irrespective of PD-L1 status. This mechanism is described across cancers and is relevant to breast. (New England Journal of Medicine)</t>
+  </si>
+  <si>
+    <t>Zaretsky et al., N Engl J Med 2016 – B2M and JAK mutations with acquired resistance to PD-1.(New England Journal of Medicine) Nowicki et al., Cancer J 2018 – mechanisms of resistance to PD-1/PD-L1 (antigen presentation loss).(PMC) Han et al., 2025 review on B2M in immunotherapy resistance.(PMC)</t>
+  </si>
+  <si>
+    <t>High LAG-3 on intratumoral T cells marks deeper exhaustion; co-expression with PD-1 defines dysfunctional T cells that respond poorly to PD-1/PD-L1 blockade alone. Upregulation of LAG-3 after PD-1/PD-L1 therapy is a recognized adaptive resistance mechanism, motivating dual PD-1/LAG-3 blockade. (PMC)</t>
+  </si>
+  <si>
+    <t>Yang et al., Oncotarget 2017 – LAG-3 expression defines exhausted intratumoral PD-1⁺ T cells.(Oncotarget) Qiu et al., 2024 (PD-1 and LAG-3 dual blockade mechanisms).(PMC) Cai et al., J Hematol Oncol 2023 – review of LAG-3, TIM-3, TIGIT &amp; co-expression as resistance.(SpringerLink)</t>
+  </si>
+  <si>
+    <t>PTEN loss and oncogenic PI3K/AKT/mTOR activation promote an immunosuppressive TME via reduced CD8⁺ T-cell infiltration and increased VEGF/cytokines. Across cancers (including breast/TNBC), PTEN/PI3K alterations are linked to poorer response to PD-1/PD-L1 blockade and are being targeted to re-sensitize tumors to ICIs. (MDPI)</t>
+  </si>
+  <si>
+    <t>Vidotto et al., Br J Cancer 2020 – PTEN loss and immune evasion, predictive of ICI resistance.(Nature) Cretella et al., Cancer Discov 2019 – PTEN and resistance to PD-1/PD-L1 therapies.(PMC) Hassan et al., Cancers 2025 – PI3K/AKT/mTOR in TNBC and immune evasion.(MDPI)</t>
+  </si>
+  <si>
+    <t>Hypoxia via HIF-1α drives VEGF-mediated abnormal vasculature, T-cell exclusion, recruitment of Tregs/MDSCs and PD-L1 upregulation on tumor and myeloid cells. High hypoxia signatures associate with immune-excluded, ICI-refractory tumors, including breast, and VEGF/HIF-1α targeting is being explored to improve PD-1/PD-L1 responses. (SpringerLink)</t>
+  </si>
+  <si>
+    <t>Wu et al., Cell Mol Life Sci 2022 – hypoxia/HIFs as master regulators of tumor immune escape.(PMC) Liu et al., 2024 – HIF-1α–VEGF axis and PD-L1, impacting PD-1/PD-L1 sensitivity.(SpringerLink)</t>
+  </si>
+  <si>
+    <t>Down (deficient)</t>
+  </si>
+  <si>
+    <t>Sensitive (with caveats)</t>
+  </si>
+  <si>
+    <t>HRD/BRCA1/2-mutated and HRD-like TNBC have increased genomic instability, higher TMB and more neoantigens, which can favor T-cell infiltration and PD-L1 expression. Multiple reviews link DDR defects to improved ICI benefit, though responses are heterogeneous and depend on co-existing immune-suppressive programs. (PubMed)</t>
+  </si>
+  <si>
+    <t>Pellegrino et al., Cancer Treat Rev 2020 – HRD and ICI sensitivity, especially in TNBC.(PubMed) Zhang et al., Biomark Res 2020 – DDR defects as ICI biomarkers.(SpringerLink) Clark et al., Front Oncol 2021 – harnessing DNA repair defects to augment immunity in TNBC.(Frontiers)</t>
+  </si>
+  <si>
+    <t>Sensitive (immune-NF-κB dominant)</t>
+  </si>
+  <si>
+    <t>When NF-κB activation is primarily in immune/myeloid/stromal cells, it drives production of CXCL9/10/11 and other inflammatory chemokines that recruit and sustain effector T-cells, supporting response to PD-1/PD-L1 blockade. However, strongly tumor-intrinsic NF-κB can promote survival and resistance, so the net effect depends on compartment and co-signatures. (PMC)</t>
+  </si>
+  <si>
+    <t>Tokunaga et al., Int J Mol Sci 2017 – CXCL9/10/11–CXCR3 axis and antitumor immunity.(PMC) House et al., Clin Cancer Res 2020 – macrophage-derived CXCL9/10 required for ICI efficacy.(AACR Journals) Vilgelm &amp; Richmond, Front Immunol 2019 – chemokines and ICI responses.(Frontiers)</t>
+  </si>
+  <si>
+    <t>IDO1 catabolizes tryptophan to kynurenine, suppressing T-cell proliferation and promoting Tregs and dysfunctional NK cells. High IDO1 expression is common in high-grade/TNBC and often co-expressed with PD-L1, contributing to resistance to PD-1/PD-L1 monotherapy; IDO1 inhibition (e.g., GDC-0919) has been combined with atezolizumab in early trials. (ScienceDirect)</t>
+  </si>
+  <si>
+    <t>Dill et al., Breast J 2018 – IDO expression frequent in high-grade TNBC and associated with PD-L1.(ScienceDirect) Huang et al., Cancers 2022 – IDO1 promotes Treg-mediated immunosuppression.(MDPI) Prendergast et al., Cancer Res 2017 – IDO1 inhibitors and phase Ib IDO1 + atezo trial.(AACR Journals) Jing et al., Breast Cancer 2024 – IDO1 impairs NK cell antitumor immunity in TNBC.(SpringerLink)</t>
+  </si>
+  <si>
+    <t>Effective CD8⁺ T-cell priming requires TCR plus CD28–CD80/86 co-stimulation and IL-2 signaling. In the absence of these signals (e.g., low CD80/86 on APCs, chronic CTLA-4 engagement, steroids), T cells become anergic or exhausted and cannot be fully re-activated by PD-L1 blockade alone, limiting atezo benefit even if PD-L1 is high. (PMC)</t>
+  </si>
+  <si>
+    <t>Esensten et al., Immunity 2016 – CD28 co-stimulation prevents T-cell anergy.(PMC) Nandi &amp; Gupta, J Biosci 2020 – T-cell co-stimulation, checkpoint inhibitors, and anti-tumor immunity.(Indian Academy of Sciences) Waldman et al., Nat Rev Immunol 2020 – T-cell biology in cancer immunotherapy.(Nature)</t>
+  </si>
+  <si>
+    <t>High Treg and MDSC signatures (FoxP3, CCR8, IL-6, IL-8, ARG1, CCL2, etc.) indicate an immunosuppressive TME that counteracts PD-L1 blockade. MDSCs and Tregs suppress CD8⁺ T-cell function, promote PD-L1 expression, and are recognized contributors to primary and acquired resistance to ICIs, including in breast cancer models. (Frontiers)</t>
+  </si>
+  <si>
+    <t>Hou et al., Front Immunol 2020 – MDSCs directly cause resistance to ICIs.(Frontiers) Wu et al., Mol Cancer 2022 – MDSCs as key promoters of immune escape.(SpringerLink) Li et al., Signal Transduct Target Ther 2021 – MDSCs in breast cancer immunosuppression.(Nature) Xu et al., Cancers 2025 – Treg checkpoints (CTLA-4, LAG-3, etc.) in invasive breast cancer.(MDPI)</t>
+  </si>
+  <si>
+    <t>HALLMARK_ALLOGRAFT_REJECTION</t>
+  </si>
+  <si>
+    <t>WP_CANCER_IMMUNOTHERAPY_BY_PD1_BLOCKADE</t>
+  </si>
+  <si>
+    <t>HALLMARK_WNT_BETA_CATENIN_SIGNALING</t>
+  </si>
+  <si>
+    <t>HALLMARK_TGF_BETA_SIGNALING</t>
+  </si>
+  <si>
+    <t>GOBP_ANTIGEN_PROCESSING_AND_PRESENTATION</t>
+  </si>
+  <si>
+    <t>GOBP_REGULATION_OF_T_CELL_ACTIVATION</t>
+  </si>
+  <si>
+    <t>HALLMARK_HYPOXIA</t>
+  </si>
+  <si>
+    <t>KEGG_HOMOLOGOUS_RECOMBINATION</t>
+  </si>
+  <si>
+    <t>GOBP_KYNURENINE_METABOLIC_PROCESS</t>
+  </si>
+  <si>
+    <t>GOBP_REGULATION_OF_T_CELL_COSTIMULATION</t>
+  </si>
+  <si>
+    <t>Treg/Myeloid Immunosuppressive Pathways (redundunt to regulatory_t_cell_activation)</t>
+  </si>
+  <si>
+    <t>Regulation (corrected – baseline)</t>
+  </si>
+  <si>
+    <t>Rationale (baseline, breast cancer–focused)</t>
+  </si>
+  <si>
+    <t>Ref(s) (corrected, descriptive)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (high VEGF-A / VEGFR, high MVD)</t>
+    </r>
+  </si>
+  <si>
+    <t>Breast tumors with high VEGF-A expression, VEGFR2 and microvessel density are strongly dependent on pathological angiogenesis. Bevacizumab neutralizes VEGF-A, normalizes/prunes vessels and limits perfusion; trials and biomarker studies in HER2-negative MBC and neoadjuvant settings indicate tumors with greater vascular density/angiogenic gene signatures derive more benefit from bevacizumab-containing regimens.</t>
+  </si>
+  <si>
+    <t>Miller KD et al., N Engl J Med 2007 (E2100, paclitaxel±bevacizumab), PMID:18160686.(PubMed) Schneider BP et al., Clin Cancer Res 2013 (tumor vascular markers &amp; E2100), PMID:23362323.(AACR Journals) Krüger K et al., Sci Rep 2021 (baseline MVD &amp; neoadjuvant bevacizumab), PMID:33479326.(Nature)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (strong hypoxia/HIF signature at baseline)</t>
+    </r>
+  </si>
+  <si>
+    <t>High HIF-1α and hypoxia signatures in breast cancer correlate with VEGF expression, aggressive biology and poor prognosis. In refractory breast cancer, bevacizumab can induce acute hypoxia with secretion of pro-angiogenic and pro-invasive cytokines, leading to early progression. Tumors already hypoxic at baseline are primed for this HIF-driven escape, so bevacizumab is less effective.</t>
+  </si>
+  <si>
+    <t>Nalwoga H et al., PLoS One 2016 (HIF-1α, VEGF and poor prognosis in breast cancer), PMID:26784867.(PLOS) Ueda S et al., Clin Cancer Res 2017 (bevacizumab induces acute hypoxia &amp; progression in refractory breast cancer), PMID:28679773.(PubMed) Carmona-Bozo JC et al., Breast Cancer Res 2020 (hypoxia &amp; perfusion in breast cancer), PMID:33246466.(PMC)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (baseline EMT-high)</t>
+    </r>
+  </si>
+  <si>
+    <t>EMT activation (loss of E-cadherin; upregulation of TWIST, SNAIL, vimentin) promotes invasion, metastasis and use of vessel co-option rather than sprouting angiogenesis. EMT-high breast tumors are less dependent on VEGF-driven neovascularization and more tolerant of hypoxia, so VEGF-A blockade with bevacizumab yields limited, often transient benefit and can select for more invasive clones.</t>
+  </si>
+  <si>
+    <t>Reviews on hypoxia-induced EMT and therapy resistance in breast cancer (e.g., Jing X et al., Mol Cancer 2019, hypoxia &amp; TME, PMID:31514707).(SpringerLink) EMT/CSC-focused BC reviews (e.g., De Heer EC et al., Cancers 2020, HIFs, angiogenesis and metabolism in breast cancer, PMID:32870818).(Europe PMC)</t>
+  </si>
+  <si>
+    <t>Notch (including DLL4–Notch) is a key regulator of tip/stalk endothelial cell fate and vessel maturation, and in tumor cells maintains stem-like properties. When Notch signaling is high at baseline, vessels and cancer stem cells can be supported in a relatively VEGF-independent manner. Anti-angiogenic resistance literature highlights Notch upregulation as a canonical escape pathway from VEGF blockade, implying bevacizumab will be less effective in Notch-high tumors (largely cross-cancer but mechanistically applicable to breast cancer).</t>
+  </si>
+  <si>
+    <t>Haibe Y et al., Front Oncol 2020 (resistance mechanisms to anti-angiogenic therapies, including Notch/DLL4), PMID:32184992.(Frontiers)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (baseline CSC/basal-like enrichment)</t>
+    </r>
+  </si>
+  <si>
+    <t>Breast cancer stem-like cells (ALDH1^high, CD44^+/CD24^−, basal-like transcriptional programs) reside in hypoxic niches, exhibit high self-renewal, and are resistant to chemo- and radiotherapy. HIF-driven pathways promote the breast CSC phenotype. Tumors enriched in these populations at baseline can survive anti-angiogenic stress and re-seed the tumor after bevacizumab, leading to poor and short-lived responses.</t>
+  </si>
+  <si>
+    <t>Semenza GL, Clin Sci 2015 (regulation of breast cancer stem cell phenotype by HIFs), PMID:26450785.(Portland Press) Palomeras S et al., Molecules 2018 (targeting BCSCs to overcome therapy resistance), PMID:30150594.(MDPI) Early proof-of-concept neoadjuvant study exploring bevacizumab effects on breast CSCs (2019 proof-of-concept trial).(ResearchGate)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In breast cancer, particularly in obesity-associated disease, high baseline FGF2 and FGFR signaling provide an alternative pro-angiogenic axis. Clinical and preclinical work from Jain’s group shows obesity promotes resistance to anti-VEGF therapy via upregulation of IL-6 and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FGF2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; blocking IL-6 or FGF2 restores sensitivity. Thus, an FGF2/FGFR-high baseline indicates that angiogenesis can be sustained despite VEGF-A neutralization by bevacizumab.</t>
+    </r>
+  </si>
+  <si>
+    <t>Incio J et al., Sci Transl Med 2018 (“Obesity promotes resistance to anti-VEGF therapy in breast cancer by up-regulating IL-6 and potentially FGF-2”), PMID:29540614.(PubMed) Omene C et al., Cancers (Basel) 2018 (anti-VEGF therapy in obesity-related breast cancer), PMID:29642479.(PMC)</t>
+  </si>
+  <si>
+    <t>High baseline Ang2 and Tie2 (and Ang2^+ vessel density) in breast cancer correlate with lymph-node invasion, poorer survival and adverse outcomes in trials that included bevacizumab. Ang2 destabilizes vessels and recruits Tie2^+ macrophages, enabling vascular remodeling and immune suppression; persistent or rebound Ang2 undermines VEGF-A blockade. Thus, an Ang2/Tie2-high baseline is a marker of poor bevacizumab benefit.</t>
+  </si>
+  <si>
+    <t>Sfiligoi C et al., Int J Cancer 2003 (Ang2 expression &amp; poor prognosis in breast cancer), PMID:12557245.(SpringerLink) Tiainen L et al., BMC Cancer 2019 (baseline Tie1/Ang2 levels &amp; poor survival in MBC), PMID:31340773 (includes bevacizumab-treated cohort, NCT00979641).(PubMed) Boucher Y et al., NPJ Precis Oncol 2021 (bevacizumab reduces Ang2^+ vessels &amp; boosts T-cell/DC infiltration in TNBC), PMID:34188163.(PubMed)</t>
+  </si>
+  <si>
+    <t>c-MET activation in breast cancer stimulates MAPK, PI3K-AKT and STAT3, drives EMT and invasion, and is associated with poor prognosis. Resistance-mechanism reviews identify HGF/c-MET as a key bypass route in tumors resistant to anti-VEGF therapy: under hypoxia, MET signaling is further induced and supports invasive escape and alternative angiogenesis. Baseline MET-high tumors are therefore less likely to respond durably to bevacizumab.</t>
+  </si>
+  <si>
+    <t>Haibe Y et al., Front Oncol 2020 (HGF/c-MET as a central axis of anti-VEGF resistance), PMID:32184992.(Frontiers) Iweala EEJ et al., Cancer Treat Res Commun 2024 (review of c-MET in breast cancer mechanisms and targeting), 2024 review.(ScienceDirect)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (T-cell–inflamed / high TILs, IFN-γ)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Sensitive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (immune-potentiated)</t>
+    </r>
+  </si>
+  <si>
+    <t>Breast tumors with high baseline TILs and T-cell inflammatory signatures (e.g., many TNBCs) can benefit from vascular normalization: bevacizumab transiently reduces Ang2^+ vasculature, lowers hypoxia and interstitial pressure, and markedly increases CD4⁺/CD8⁺ T-cell and mature dendritic-cell infiltration. This suggests a T-cell–inflamed baseline microenvironment is favorable for bevacizumab-mediated immune enhancement and synergy with chemotherapy or ICIs.</t>
+  </si>
+  <si>
+    <t>Boucher Y et al., NPJ Precis Oncol 2021 (bevacizumab improves tumor infiltration of mature DCs and effector T cells in primary TNBC), PMID:34188163.(PubMed)</t>
+  </si>
+  <si>
+    <t>IL-6/STAT3 signaling drives a pro-angiogenic, immunosuppressive milieu through VEGF/FGF2 induction and recruitment of myeloid cells. In obesity-associated breast cancer, high baseline IL-6 and FGF2 levels were strongly associated with resistance to anti-VEGF therapy; IL-6 blockade normalized vessels and restored sensitivity in mouse models. Thus, an IL-6/STAT3-high baseline is a negative predictive factor for bevacizumab.</t>
+  </si>
+  <si>
+    <t>Incio J et al., Sci Transl Med 2018 (IL-6/FGF2 mediate anti-VEGF resistance in obese breast cancer), PMID:29540614.(PubMed) Omene C et al., Cancers (Basel) 2018 (review on anti-VEGF therapy and obesity in breast cancer), PMID:29642479.(PMC)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (high composite angiogenesis gene set)</t>
+    </r>
+  </si>
+  <si>
+    <t>A high “angiogenesis” gene signature (e.g., VEGF, ANGPTL4, PECAM1, endothelial markers) at baseline indicates that tumor growth is tightly coupled to neovascularization. Breast cancer gene-expression studies and tissue-based angiogenesis markers show that angiogenesis-high tumors (high MVD/angiogenic profile) are more likely to benefit from bevacizumab-containing therapy than angiogenesis-low tumors.</t>
+  </si>
+  <si>
+    <t>Mendiola M et al., Oncotarget 2016 (angiogenesis-related gene profiling in HER2-negative MBC treated with bevacizumab + weekly paclitaxel), PMID:26992213.(PMC) Krüger K et al., Sci Rep 2021 (baseline MVD &amp; bevacizumab response in neoadjuvant HER2-negative breast cancer), PMID:33479326.(Nature) Tolaney SM et al., PNAS 2015 (role of vascular density/normalization and bevacizumab benefit), PMID:26733601.(PNAS)</t>
+  </si>
+  <si>
+    <r>
+      <t>Down</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (low FGF2, PDGFs, Ang2, PlGF at baseline)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">When alternative pro-angiogenic pathways (FGF2/FGFR, PDGFs, Ang2, PlGF) are low at baseline, VEGF-A is the dominant driver of angiogenesis. In this “VEGF-addicted but FGF/Ang2-quiet” setting, bevacizumab shuts down the main angiogenic axis and there are few bypass options, leading to better and more durable responses. This is essentially the inverse of biomarker profiles where </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>high</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> FGF2 or Ang2 predicts poor anti-VEGF benefit.</t>
+    </r>
+  </si>
+  <si>
+    <t>Same data sources as for FGF2- and Ang2-high resistance, interpreted inversely: Incio J et al., Sci Transl Med 2018, PMID:29540614.(PubMed) Tiainen L et al., BMC Cancer 2019 (high Ang2/Tie1 associated with poor survival), PMID:31340773.(PubMed)</t>
+  </si>
+  <si>
+    <t>Some breast tumors show low angiogenic activity and rely on co-opting pre-existing vessels, or are very slowly growing with low MVD. In such “angiogenesis-off” tumors there is little VEGF-driven neovascularization for bevacizumab to target; clinical and imaging studies of anti-angiogenic therapy indicate these lesions gain minimal benefit, representing intrinsic non-response despite VEGF-A blockade.</t>
+  </si>
+  <si>
+    <t>Haibe Y et al., Front Oncol 2020 (overview of resistance mechanisms to anti-angiogenic therapy, including vessel co-option/angiogenic dormancy), PMID:32184992.(Frontiers) Jing X et al., Mol Cancer 2019 (hypoxia &amp; microenvironmental adaptations underlying therapy resistance), PMID:31514707.(SpringerLink)</t>
+  </si>
+  <si>
+    <t>KEGG_VEGF_SIGNALING_PATHWAY</t>
+  </si>
+  <si>
+    <t>HALLMARK_EPITHELIAL_MESENCHYMAL_TRANSITION</t>
+  </si>
+  <si>
+    <t>REACTOME_SIGNALING_BY_NOTCH</t>
+  </si>
+  <si>
+    <t>SMID_BREAST_CANCER_BASAL_UP</t>
+  </si>
+  <si>
+    <t>PID_FGF_PATHWAY</t>
+  </si>
+  <si>
+    <t>REACTOME_TIE2_SIGNALING</t>
+  </si>
+  <si>
+    <t>REACTOME_SIGNALING_BY_MET</t>
+  </si>
+  <si>
+    <t>REACTOME_SIGNALING_BY_PDGF</t>
+  </si>
+  <si>
+    <r>
+      <t>Down</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (intrinsically low VEGF/angiogenesis; vessel co-option)</t>
+    </r>
+  </si>
+  <si>
+    <t>Angiogenic Dormancy / Vessel Co-option – Downregulated Angiogenesis (repeat of hallmark angeogeneis)</t>
+  </si>
+  <si>
+    <t>Regulation (corrected, baseline)</t>
+  </si>
+  <si>
+    <t>Upregulated (hyperactive PI3K–AKT–mTOR due to PIK3CA/AKT1 mutations or PTEN loss)</t>
+  </si>
+  <si>
+    <t>HR+/HER2− metastatic breast cancers with PI3K/AKT1/PTEN alterations show greater benefit from capivasertib + fulvestrant vs fulvestrant alone; presurgical dosing shows strong pAKT and Ki-67 suppression in AKT-addicted ER+ tumours, consistent with oncogene addiction to this pathway.</t>
+  </si>
+  <si>
+    <t>Turner et al., N Engl J Med 2023;388:2058–2070. PMID: 37256976 (CAPItello-291); Jones et al., Lancet Oncol 2020;21:345–357. PMID: 32035020 (FAKTION); Robertson et al., Clin Cancer Res 2020;26:1574–1585. PMID: 31836609 (STAKT).</t>
+  </si>
+  <si>
+    <t>In PIK3CA- or PTEN-altered ER+ models, capivasertib efficacy is FOXO3-dependent; FOXO3A deletion reduces response and is accompanied by FOXM1 upregulation, whereas preserved FOXO3 enables cell-cycle arrest and apoptosis after AKT inhibition.</t>
+  </si>
+  <si>
+    <t>Cutano et al., npj Breast Cancer 2025;11:36. PMID: 40263319; Robertson et al., Clin Cancer Res 2020;26:1574–1585. PMID: 31836609.</t>
+  </si>
+  <si>
+    <t>Upregulated FOXM1/E2F and G2M signatures</t>
+  </si>
+  <si>
+    <t>Long-term AKT inhibition (including capivasertib) induces FOXM1 upregulation; FOXM1 overexpression attenuates capivasertib’s anti-proliferative effects, while FOXM1 knockdown restores sensitivity, so high FOXM1/E2F/G2M programme marks cells that continue cycling under AKT blockade.</t>
+  </si>
+  <si>
+    <t>Cutano et al., npj Breast Cancer 2025;11:36. PMID: 40263319; Ros et al., Cancer Cell 2020;38:516–533.e9.</t>
+  </si>
+  <si>
+    <t>Upregulated MAPK/ERK activity (RTK/RAS-driven)</t>
+  </si>
+  <si>
+    <t>PI3K/AKT pathway inhibition frequently triggers feedback activation of RTKs and ERK, providing an alternative growth and survival route; elevated MAPK signatures or driver alterations decrease dependence on AKT and limit benefit from AKT inhibitors unless co-targeted.</t>
+  </si>
+  <si>
+    <t>Martorana et al., Front Pharmacol 2021;12:662232; Coleman et al., Cancers (Basel) 2021;13:5748.</t>
+  </si>
+  <si>
+    <t>Upregulated SGK1/PDK1–SGK1 axis</t>
+  </si>
+  <si>
+    <t>Breast cancer cell lines with high SGK1 show innate resistance to AKT inhibitors (including AZD5363/capivasertib); SGK1 knockdown selectively impairs growth of AKT-inhibitor-resistant cells, and SGK1 can maintain mTORC1 via TSC2 even when AKT is blocked.</t>
+  </si>
+  <si>
+    <t>Sommer et al., Biochem J 2013;452:499–508. PMID: 23581296; Castel et al., Cancer Cell 2016;30:1–15.</t>
+  </si>
+  <si>
+    <t>Upregulated and/or persistently active mTORC1-driven translation (e.g. high p-4EBP1, ribosomal proteins)</t>
+  </si>
+  <si>
+    <t>Short-term biomarker studies show that incomplete suppression of mTORC1 and translational output despite AKT inhibition is associated with weaker anti-proliferative effects; SGK1–TSC2–mTORC1 signalling can maintain protein synthesis independently of AKT.</t>
+  </si>
+  <si>
+    <t>Robertson et al., Clin Cancer Res 2020;26:1574–1585. PMID: 31836609; Castel et al., Cancer Cell 2016;30:1–15.</t>
+  </si>
+  <si>
+    <t>Upregulated ER pathway (ER-positive, endocrine-driven tumour)</t>
+  </si>
+  <si>
+    <t>Sensitive (to fulvestrant + capivasertib in PI3K/AKT/PTEN-altered ER+ disease)</t>
+  </si>
+  <si>
+    <t>Capivasertib trials are in ER+/HER2− disease where ER signalling is active at baseline; FAKTION and CAPItello-291 show improved PFS with capivasertib + fulvestrant, particularly in tumours harbouring PI3K/AKT1/PTEN alterations, consistent with ER-driven tumours relying on both ER and PI3K–AKT survival axes which can be co-targeted.</t>
+  </si>
+  <si>
+    <t>Jones et al., Lancet Oncol 2020;21:345–357. PMID: 32035020; Turner et al., N Engl J Med 2023;388:2058–2070. PMID: 37256976; Burstein &amp; Hanker, J Clin Oncol 2024 (review of ER–PI3K/AKT cross-talk).</t>
+  </si>
+  <si>
+    <t>Downregulated / lost FOXO3 activity and pro-apoptotic output</t>
+  </si>
+  <si>
+    <t>FOXO3A loss-of-function in PIK3CA-altered ER+ models blunts capivasertib-induced cell-cycle arrest and apoptosis; low FOXO3 or impaired FOXO3 nuclear signalling removes the apoptotic execution arm required for effective killing by AKT inhibition.</t>
+  </si>
+  <si>
+    <t>Downregulated FOXM1 / lower mitotic drive</t>
+  </si>
+  <si>
+    <t>FOXM1 downregulation is associated with response to PI3K/AKT pathway inhibition; silencing FOXM1 restores sensitivity to capivasertib in resistant models, whereas FOXM1 overexpression diminishes drug efficacy, so lower FOXM1/mitotic drive favours durable arrest and death under AKT blockade.</t>
+  </si>
+  <si>
+    <t>Downregulated MAPK/RTK (RAS/HER2) signalling or co-inhibited (e.g. anti-HER2, MEK inhibitor)</t>
+  </si>
+  <si>
+    <t>When MAPK/RTK pathways are low or co-targeted, tumours become more dependent on PI3K–AKT; preclinical breast models show enhanced anti-tumour activity with capivasertib plus anti-HER2 or MEK/RTK inhibitors, consistent with removal of bypass routes and greater vulnerability to AKT blockade.</t>
+  </si>
+  <si>
+    <t>Andrikopoulou et al., Breast 2022;62:xx–xx (review of capivasertib in breast cancer); Martorana et al., Front Pharmacol 2021;12:662232.</t>
+  </si>
+  <si>
+    <t>Not established as a validated predictive biomarker (TIL-high vs TIL-low exploratory only)</t>
+  </si>
+  <si>
+    <t>Effect on capivasertib response uncertain / not validated</t>
+  </si>
+  <si>
+    <t>PI3K/AKT/mTOR signalling can modulate antigen presentation and PD-L1, and AKT inhibition may in principle enhance immune susceptibility; however, in breast cancer capivasertib trials, benefit is driven by tumour PI3K/AKT/PTEN alterations rather than immune gene signatures, so IFNγ/TIL patterns are currently hypothesis-generating only.</t>
+  </si>
+  <si>
+    <t>Martorana et al., Front Pharmacol 2021;12:662232; Andrikopoulou et al., Breast 2022;62:xx–xx (no validated immune biomarker for capivasertib).</t>
+  </si>
+  <si>
+    <t>Immune Infiltration / IFNγ Pathways – ImmunoSigDB IFNγ_response, TIL-related signatures (repsonse not established)</t>
+  </si>
+  <si>
+    <t>Upregulated FOXO3 (capacity for activation upon AKT inhibition)</t>
+  </si>
+  <si>
+    <t>PID_FOXO_PATHWAY</t>
+  </si>
+  <si>
+    <t>PID_PI3KCI_PATHWAY</t>
+  </si>
+  <si>
+    <t>FOXM1 / Cell-Cycle Pathway (inverse of FOXM1–E2F row) (repeat-inverse of hallmark_e2f_target)</t>
+  </si>
+  <si>
+    <t>Rationale (correct, baseline pre-Dostarlimab)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up / active</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (PD-1⁺ TILs, PD-L1⁺ tumor/immune cells)</t>
+    </r>
+  </si>
+  <si>
+    <t>Sensitive (MoA/biomarker)</t>
+  </si>
+  <si>
+    <t>In breast tumors where dostarlimab is considered (e.g. TNBC, dMMR, TMB-high), the PD-1/PD-L1 axis is typically engaged: PD-1 is expressed on exhausted TILs and PD-L1 on tumor and myeloid cells. Dostarlimab (anti-PD-1 IgG4) binds PD-1 and blocks PD-L1/PD-L2, releasing this inhibitory brake and restoring T-cell cytotoxicity. Baseline PD-L1 expression and TIL-rich TNBC are associated with benefit from PD-1/PD-L1 blockade.</t>
+  </si>
+  <si>
+    <t>Dostarlimab MoA: Costa et al., 2022, “Dostarlimab: A Review” (humanized IgG4 anti-PD-1).(PMC) DrugBank DB15627 (dostarlimab).(DrugBank) PD-1/PD-L1 blockade in breast cancer (TNBC trials, biomarker discussion).(PMC)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up / intact</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> TCR signaling, costimulation, and TILs</t>
+    </r>
+  </si>
+  <si>
+    <t>A functional, clonally expanded T-cell repertoire with active TCR signaling and costimulation (CD28, ICOS) underlies effective PD-1 blockade. TNBC and other immunogenic breast cancers with high TILs and T-cell–inflamed gene expression signatures respond better to PD-1/PD-L1 inhibitors than immune-cold tumors with poor T-cell infiltration or anergic T cells.</t>
+  </si>
+  <si>
+    <t>T-cell-inflamed gene expression profile (IFN-γ–responsive T-cell signature) predicts response to pembrolizumab across cancers and in TNBC subsets.(PMC) Reviews of predictive biomarkers and TIL biology in TNBC.(ScienceDirect)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (T-cell-inflamed / IFN-γ-high)</t>
+    </r>
+  </si>
+  <si>
+    <t>An IFN-γ–driven microenvironment (e.g. upregulation of CXCL9/10, IDO1, HLA class I genes, STAT1 targets) defines “hot” tumors enriched for effector CD8⁺ T cells and is consistently associated with higher response rates to PD-1 blockade, including in TNBC treated with pembrolizumab or atezolizumab. Baseline IFN-γ signatures therefore support dostarlimab sensitivity.</t>
+  </si>
+  <si>
+    <t>IFN-γ-related 18-gene T-cell-inflamed GEP associated with response to pembrolizumab.(PMC) Reviews of IFN-γ/T-cell-inflamed signatures and ICI benefit in breast cancer.(ScienceDirect)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (DNA damage–induced STING/Type-I IFN)</t>
+    </r>
+  </si>
+  <si>
+    <t>HRD/BRCA-mutated breast cancers accumulate cytosolic DNA, activating cGAS–STING and type-I IFN signaling, which recruits CD8⁺ T cells and promotes an inflamed TME. Preclinical BRCA-deficient TNBC models show that STING activation via DNA damage (e.g. PARP inhibitors) is critical for optimal antitumor immunity and improves response to PD-1/PD-L1 blockade. High cGAS–STING scores correlate with genomic instability and immune cell infiltration in BC.</t>
+  </si>
+  <si>
+    <t>STING activation in BRCA-deficient TNBC and its requirement for CD8⁺ T-cell–mediated response to PARPi + ICI.(Nature) cGAS–STING expression correlates with HRD and immune infiltration in breast cancer.(PMC) DNA damage &amp; STING review in cancer immunotherapy.(Cell)</t>
+  </si>
+  <si>
+    <r>
+      <t>Down / lost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (e.g. B2M, HLA, TAP defects)</t>
+    </r>
+  </si>
+  <si>
+    <t>If baseline antigen presentation is lost, CD8⁺ T cells cannot recognize and kill tumor cells, even if PD-1 is blocked. Loss-of-function mutations in JAK1/2 or B2M and downregulation of HLA class I components are repeatedly linked to primary or acquired resistance to PD-1 blockade; these mechanisms are described across multiple tumor types and are relevant to breast cancers with low MHC-I expression.</t>
+  </si>
+  <si>
+    <t>JAK1/2 loss and B2M/HLA defects as mechanisms of resistance to anti-PD-1.(PMC) ICI resistance mechanism reviews summarizing antigen presentation loss.(SpringerLink)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (tumor + stromal TGF-β / SMAD activation)</t>
+    </r>
+  </si>
+  <si>
+    <t>High TGF-β in tumor and stromal compartments promotes EMT, fibrosis, Treg and MDSC accumulation and a strongly immune-excluded phenotype. In preclinical breast cancer and pan-tumor data, TGF-β-high tumors show poor CD8⁺ T-cell penetration and limited benefit from PD-1/PD-L1 blockade; combining TGF-β inhibitors or TGF-β/PD-L1 bispecifics with ICIs can restore intratumoral T cells and antitumor activity.</t>
+  </si>
+  <si>
+    <t>TGF-β as predictor and therapeutic target for PD-1/PD-L1 immunotherapy.(PMC) Anti-TGF-β/PD-L1 bispecific antibody improves T-cell infiltration and response in breast cancer models.(Journal of Infection and Chemotherapy)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (tumor-intrinsic WNT/β-catenin activation)</t>
+    </r>
+  </si>
+  <si>
+    <t>Activated WNT/β-catenin signaling in tumor cells suppresses recruitment/activation of dendritic cells and leads to non-T-cell-inflamed, CD8-poor TMEs. Across solid tumors, WNT/β-catenin activation correlates with immune exclusion and lack of benefit from ICIs; this mechanism likely contributes to immune-cold basal-like or luminal breast cancers with poor ICI responses.</t>
+  </si>
+  <si>
+    <t>WNT/β-catenin pathway activation linked to immune exclusion and ICI resistance across cancers.(Nature) WNT/β-catenin–immunotherapy resistance reviews.(ScienceDirect)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (e.g. PTEN loss, PIK3CA/AKT activation)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Resistant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (immune escape)</t>
+    </r>
+  </si>
+  <si>
+    <t>PTEN loss and PI3K–AKT–mTOR hyperactivation increase PD-L1 and immunosuppressive cytokines, reduce TIL infiltration and drive immune evasion. In TNBC and HR⁺/HER2⁻ breast cancer, PTEN loss is associated with poor prognosis and reduced sensitivity to checkpoint blockade; dual targeting of PI3K and PD-1/PD-L1 is being explored to overcome this resistance.</t>
+  </si>
+  <si>
+    <t>PI3K–AKT–mTOR in TNBC and links to immune evasion and PD-1/PD-L1 resistance.(PMC) PTEN loss as predictive biomarker of ICI resistance.(Nature)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (TIM-3⁺ exhausted T cells/Tregs, often after PD-1 axis engagement)</t>
+    </r>
+  </si>
+  <si>
+    <t>Resistant / adaptive resistance</t>
+  </si>
+  <si>
+    <t>HAVCR2 (TIM-3) is upregulated on chronically stimulated, exhausted CD8⁺ T cells and on Tregs in many tumors. During PD-1 therapy, TIM-3 expression often increases on PD-1-bound T cells via PI3K/AKT-dependent mechanisms, providing a compensatory inhibitory signal and mediating adaptive resistance to PD-1 blockade. High TIM-3 at baseline or on-treatment in breast-like immune-excluded TMEs is therefore a negative predictor for single-agent dostarlimab.</t>
+  </si>
+  <si>
+    <t>TIM-3 upregulation during PD-1 blockade and reversal by combined PD-1/TIM-3 inhibition.(PubMed) Reviews of TIM-3/PD-1 compensatory checkpoint biology.(SpringerLink)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (high IDO1, KYN/Trp ratio)</t>
+    </r>
+  </si>
+  <si>
+    <t>Tumor and myeloid IDO1 catabolize tryptophan to kynurenine, which suppresses effector T-cell and NK-cell function and promotes Treg differentiation. IDO1 expression is common in high-grade TNBC and frequently co-expressed with PD-L1, supporting an IDO-driven immunosuppressive state that blunts PD-1 blockade. High baseline IDO1 therefore predicts decreased sensitivity to single-agent dostarlimab, motivating IDO1 + PD-1 combination strategies.</t>
+  </si>
+  <si>
+    <t>IDO1 biology and its role in immune evasion and ICI resistance.(SpringerLink) IDO1 expression and PD-L1 co-expression in TNBC.(ScienceDirect) Kynurenine pathway in breast cancer immune suppression.(PMC)</t>
+  </si>
+  <si>
+    <r>
+      <t>Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (IL-10, TGF-β, etc.)</t>
+    </r>
+  </si>
+  <si>
+    <t>Elevated IL-10 (often with TGF-β and other suppressive cytokines) promotes Treg expansion, MDSC function and suppression of antigen-presenting cells, maintaining a “cold” or immune-dysfunctional TME. Such cytokine-high tumors show attenuated benefit from PD-1/PD-L1 blockade; durable responses often require either re-programming of myeloid/cytokine networks or combination strategies.</t>
+  </si>
+  <si>
+    <t>Reviews of resistance to PD-1/PD-L1 blockade highlighting immunosuppressive cytokine milieus (IL-10, TGF-β) as mechanisms of non-response.(SpringerLink)</t>
+  </si>
+  <si>
+    <r>
+      <t>Down / defective</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (JAK1/2, IFNγR, STAT mutations or downregulation)</t>
+    </r>
+  </si>
+  <si>
+    <t>Anti-PD-1–activated T cells depend on intact IFN-γ–JAK–STAT signaling in tumor cells to upregulate antigen presentation, chemokines and pro-apoptotic programs. Loss-of-function JAK1/2 or IFNγR mutations abolish tumor cell responsiveness to IFN-γ and have been directly linked to primary and acquired resistance to PD-1 blockade in melanoma and dMMR cancers; analogous defects would be expected to confer resistance to dostarlimab in breast tumors.</t>
+  </si>
+  <si>
+    <t>JAK1/2 LoF mutations causing IFN-γ insensitivity and resistance to anti-PD-1.(PubMed) ICI resistance reviews summarizing IFN-JAK–STAT defects.(SpringerLink)</t>
+  </si>
+  <si>
+    <t>REACTOME_CO_INHIBITION_BY_PD_1</t>
+  </si>
+  <si>
+    <t>KEGG_T_CELL_RECEPTOR_SIGNALING_PATHWAY</t>
+  </si>
+  <si>
+    <t>KEGG_MEDICUS_REFERENCE_CGAS_STING_SIGNALING_PATHWAY</t>
+  </si>
+  <si>
+    <t>GOBP_ANTIGEN_PROCESSING_AND_PRESENTATION_OF_PEPTIDE_ANTIGEN_VIA_MHC_CLASS_I</t>
+  </si>
+  <si>
+    <t>GOBP_TOLERANCE_INDUCTION_DEPENDENT_UPON_IMMUNE_RESPONSE</t>
+  </si>
+  <si>
+    <t>GOBP_L_TRYPTOPHAN_CATABOLIC_PROCESS_TO_KYNURENINE</t>
+  </si>
+  <si>
+    <t>REACTOME_INTERLEUKIN_10_SIGNALING</t>
+  </si>
+  <si>
+    <t>KEGG_JAK_STAT_SIGNALING_PATHWAY</t>
+  </si>
+  <si>
+    <t>Regulation (baseline, corrected)</t>
+  </si>
+  <si>
+    <t>Rationale (correct, breast-cancer specific)</t>
+  </si>
+  <si>
+    <t>HALLMARK_ESTROGEN_RESPONSE_EARLY / HALLMARK_ESTROGEN_RESPONSE_LATE</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elacestrant is an oral SERD that degrades ERα, suppresses ER-regulated transcription, and inhibits growth of ER+/HER2– cell lines and PDXs. Tumors with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>high baseline estrogen-response signatures</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (strong ER program, often including ESR1 mutations) remain ER-addicted and derive greater benefit when this program is shut down by elacestrant. EMERALD showed the largest PFS gain in ESR1-mutated, ER-driven tumors, consistent with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Up estrogen-response → sensitivity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bihani et al., Clin Cancer Res 2017, elacestrant preclinical PDXs, PMID:28473534.(PubMed) Pancholi et al., NPJ Breast Cancer 2022, ESR1-mutant endocrine-resistant PDXs, PMID:36446866.(PubMed) Bidard et al., EMERALD phase III, J Clin Oncol 2022, PMID:35584336; NCT03778931.(PubMed) EstroGene/EstroGene2.0 ER-program datasets.(PMC)</t>
+  </si>
+  <si>
+    <t>R-HSA-9018519 – Estrogen-dependent gene expression (Reactome)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">This Reactome pathway represents canonical ER target-gene transcription. Elacestrant degrades ER and suppresses estrogen-dependent gene expression in vitro and in ER+ PDX models. Tumors with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>strong baseline activation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of this pathway remain transcriptionally ER-dependent and are more likely to respond when elacestrant extinguishes this program.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bihani et al., Clin Cancer Res 2017, PMID:28473534.(PubMed) Pancholi et al., NPJ Breast Cancer 2022, PMID:36446866.(PubMed) Abba et al., ERα-status gene expression, BMC Genomics 2005, PMID:15790392.(SpringerLink)</t>
+  </si>
+  <si>
+    <t>hsa04915 – Estrogen signaling pathway (KEGG)</t>
+  </si>
+  <si>
+    <t>Up (baseline ER/ESR1-driven, often ESR1-mutant)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">KEGG estrogen-signaling integrates ER genomic and non-genomic outputs. In metastatic ER+/HER2– disease, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ESR1 mutations maintain or enhance estrogen-signaling despite AIs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; EMERALD demonstrated a clinically meaningful PFS improvement with elacestrant vs standard endocrine therapy, particularly in ESR1-mutant tumors, indicating that </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>high estrogen-signaling dependence → elacestrant sensitivity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, even in AI-resistant settings.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bidard et al., EMERALD, J Clin Oncol 2022, PMID:35584336; NCT03778931.(PubMed) Brett et al., ESR1 mutations in MBC, Breast Cancer Res 2021, PMID:33602230.(SpringerLink) Hoy, Elacestrant first approval, Drugs 2023, PMID:36995533.(SpringerLink)</t>
+  </si>
+  <si>
+    <t>HALLMARK_ESTROGEN_RESPONSE_EARLY/LATE (relapse)</t>
+  </si>
+  <si>
+    <t>Down (baseline in endocrine-relapsed or ER-low clones)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Multi-omic datasets of endocrine-resistant ER+ breast cancer show that relapsed tumors and resistant clones often have </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reduced estrogen-response gene-set scores and attenuated ER program</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, with a shift toward alternative signaling and metabolic pathways; such tumors are less dependent on ER and show poorer response to further endocrine/SERD therapy, including elacestrant.</t>
+    </r>
+  </si>
+  <si>
+    <t>Schagerholm Stanev et al., Transcriptomic profiles of endocrine-resistant breast cancer, BMC Cancer 2025, DOI:10.1186/s12885-025-14826-1.(PMC) EstroGene2.0 ER-modulator response database.(PMC) Jones et al., Sci Rep 2025, gene expression and endocrine resistance, PMID:40021703.(PubMed)</t>
+  </si>
+  <si>
+    <t>Up (high proliferation / E2F-driven)</t>
+  </si>
+  <si>
+    <r>
+      <t>Sensitive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(mechanistically plausible but not yet a validated biomarker)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elacestrant downregulates cell-cycle regulators and proliferation markers, including E2F-regulated genes, in ER+ and CDK4/6i-resistant models, leading to growth inhibition and cell-cycle arrest. Baseline </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>high E2F-target expression</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> reflects a strongly proliferative, ER-cyclin D–CDK4/6-driven state that elacestrant can partially shut down; such tumors often remain endocrine-dependent despite prior CDK4/6i, so </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Up E2F → more substrate for elacestrant’s antiproliferative effect</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (recognizing that very extreme proliferation can also mark more aggressive biology).</t>
+    </r>
+  </si>
+  <si>
+    <t>Patel et al., Breast Cancer Res 2019, CDK4/6i-resistant models, PMID:31852484.(PubMed) Pancholi et al., NPJ Breast Cancer 2022, PMID:36446866.(PubMed) Giugliano et al., CDK4/6i resistance review, Crit Rev Oncol Hematol 2025.(ScienceDirect)</t>
+  </si>
+  <si>
+    <t>HALLMARK_G2M_CHECKPOINT / hsa04110 – Cell cycle</t>
+  </si>
+  <si>
+    <t>Up (high G2/M and cell-cycle activity)</t>
+  </si>
+  <si>
+    <r>
+      <t>Sensitive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(with caveats)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Preclinical elacestrant studies show robust suppression of proliferation, reduced Ki-67, and tumor regression in multiple ER+ cell lines and PDXs, including those with prior CDK4/6i exposure. Baseline </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>elevated G2/M and cell-cycle gene expression</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> indicates actively cycling, ER-driven luminal tumors; such tumors provide more proliferative substrate for elacestrant to arrest, so </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Up G2/M → relative sensitivity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, although very aggressive, highly proliferative clones may harbor additional resistance mechanisms.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bihani et al., Clin Cancer Res 2017, PMID:28473534.(PubMed) Patel et al., Breast Cancer Res 2019, PMID:31852484.(PubMed) EMERALD subgroup analyses confirming benefit after CDK4/6i, JCO 2024 update.(PubMed)</t>
+  </si>
+  <si>
+    <t>HALLMARK_PI3K_AKT_MTOR_SIGNALING / HALLMARK_MTORC1_SIGNALING</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hyperactivation of PI3K/AKT/mTOR (via PIK3CA mutation, PTEN loss, RTK activation) is a well-established mechanism of endocrine resistance in ER+ MBC. Genomic profiling of endocrine-resistant disease shows frequent PI3K pathway alterations at progression; these lesions provide ER-independent survival signals and blunt the efficacy of ER-targeted agents, including SERDs. Preclinical data show that combining elacestrant with PI3K or mTOR inhibitors can resensitize such tumors, implying that </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>baseline Up PI3K/AKT/mTOR is a resistance factor for elacestrant monotherapy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, partially overcome in rational combinations.</t>
+    </r>
+  </si>
+  <si>
+    <t>Razavi et al., genomic landscape of endocrine-resistant ER+ MBC, Nat Genet 2018, PMID:30510239.(PMC) Raheem et al., endocrine resistance review, Int J Mol Sci 2023, PMID:37948003.(MDPI) Gerratana et al., ESR1/PIK3CA codon variants in HR+/HER2– MBC, Breast Cancer Res 2023, PMID:36977719.(SpringerLink) Bihani et al. &amp; Patel et al. combination data with everolimus / CDK4/6i.(PubMed)</t>
+  </si>
+  <si>
+    <t>HALLMARK_PI3K_AKT_MTOR_SIGNALING / hsa04151 – PI3K-Akt signaling</t>
+  </si>
+  <si>
+    <t>Up (baseline or acquired)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Independent of the mTORC1 subset, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>global PI3K–Akt activation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (PIK3CA mutations, AKT activation, PTEN loss) is repeatedly linked with poor endocrine therapy response and earlier relapse. Clinical and translational series show higher rates of PI3K pathway alterations in endocrine-resistant vs sensitive ER+ tumors; these alterations attenuate dependence on ER, so </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Up PI3K-Akt → reduced elacestrant benefit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> relative to PI3K-wild-type disease, though EMERALD still shows some PFS gain in such subgroups.</t>
+    </r>
+  </si>
+  <si>
+    <t>Razavi et al., Nat Genet 2018, PMID:30510239.(PMC) Tolaney et al., ESR1 and PIK3CA mutations in endocrine-treated BC, npj Breast Cancer 2022, PMID:35580865.(PMC) He et al., PI3K/Akt signaling review, Signal Transduct Target Ther 2021, PMID:34362877.(Nature) EMERALD subgroup analyses, JCO/Ann Oncol 2022–2024.(Annals of Oncology)</t>
+  </si>
+  <si>
+    <t>ErbB/RTK signaling (e.g. hsa04012 – ErbB signaling pathway; HER2/EGFR/FGFR)</t>
+  </si>
+  <si>
+    <t>Resistant (class-level extrapolation to elacestrant)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Upregulated HER2/EGFR/FGFR and broader RTK signaling provides strong mitogenic and survival input that can </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bypass ER dependence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, producing HER2-enriched / Luminal-to-HER2-like phenotypes with poor response to endocrine therapy alone. Multiple preclinical and clinical datasets link RTK activation and FGFR1 amplification to endocrine resistance in ER+ breast cancer; by class extrapolation, tumors with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>high RTK signaling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> are less likely to be controlled by elacestrant monotherapy, and typically require combination strategies (e.g., anti-HER2/FGFR + SERD).</t>
+    </r>
+  </si>
+  <si>
+    <t>Servetto et al., FGFR signaling and endocrine resistance, Cancers 2021, PMID:34303787.(PubMed) Frontiers/MDPI reviews on FGFR in ER+ BC and endocrine resistance.(Frontiers) Decoding breast-cancer pathways review 2025 (HER2/RTK cross-talk), 2025 review.(ResearchGate)</t>
+  </si>
+  <si>
+    <t>Apoptosis pathways (HALLMARK_APOPTOSIS)</t>
+  </si>
+  <si>
+    <t>Down (anti-apoptotic / apoptosis-blunted state)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Estrogen signaling promotes survival by modulating pro- and anti-apoptotic gene expression; endocrine therapies and SERDs are most effective when ER+ cells are </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>primed for apoptosis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Transcriptomic studies show that endocrine-resistant ER+ tumors frequently exhibit increased survival signaling and reduced pro-apoptotic gene expression. Consequently, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>baseline low HALLMARK_APOPTOSIS activity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (strong anti-apoptotic bias) is expected to correlate with poor ability to execute cell death after ER degradation, i.e. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>relative resistance to elacestrant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, even if ER signaling is biochemically suppressed.</t>
+    </r>
+  </si>
+  <si>
+    <t>Frasor et al., estrogen up- and down-regulated genes (proliferation and apoptosis), Endocrinology 2003, PMID:12959972.(OUP Academic) Raheem et al., endocrine resistance mechanisms, Int J Mol Sci 2023, PMID:37948003.(MDPI) Li et al., transcriptomic/proteomic analyses of endocrine resistance, IJMS 2022, PMID:36142452.(MDPI)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -875,6 +3109,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -897,7 +3139,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -936,6 +3178,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1270,16 +3522,559 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBA3F18-2088-485A-86C4-2ECCC7AACBA1}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="57.08984375" customWidth="1"/>
+    <col min="2" max="2" width="36.81640625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="34.6328125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="38.36328125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" tooltip="Alpelisib for PIK3CA-Mutated, Hormone Receptor-Positive ..." display="https://pubmed.ncbi.nlm.nih.gov/31091374/?utm_source=chatgpt.com" xr:uid="{A6441139-4B5A-443B-912E-E9F8FFD4519C}"/>
+    <hyperlink ref="F3" r:id="rId2" tooltip="_x000a_            Mechanisms of Resistance to PI3K Inhibitors in Cancer: Adaptive Responses, Drug Tolerance and Cellular Plasticity - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC8037590/" xr:uid="{90CAEBC1-18BD-4AA1-92EB-7CF1A821D599}"/>
+    <hyperlink ref="F4" r:id="rId3" tooltip="A Phase I Study of Alpelisib in Combination with Trastuzumab ..." display="https://pubmed.ncbi.nlm.nih.gov/33947692/?utm_source=chatgpt.com" xr:uid="{861CB97A-7260-4140-BD4B-DDD71A9EB749}"/>
+    <hyperlink ref="F5" r:id="rId4" tooltip="Alpelisib for PIK3CA-Mutated, Hormone Receptor-Positive ..." display="https://pubmed.ncbi.nlm.nih.gov/31091374/?utm_source=chatgpt.com" xr:uid="{8A37E234-813C-41FD-AF57-B758FFB3FAD3}"/>
+    <hyperlink ref="F6" r:id="rId5" tooltip="PIK3CA mutation-driven immune signature as a prognostic ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC10927816/?utm_source=chatgpt.com" xr:uid="{5B9E55B5-AC01-4784-BFC7-833FF9D8BB6E}"/>
+    <hyperlink ref="F7" r:id="rId6" tooltip="Metabolic Imaging Detects Resistance to PI3Kα Inhibition ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC7562820/?utm_source=chatgpt.com" xr:uid="{F708B21A-B654-4FDC-B4E4-F67DF785A925}"/>
+    <hyperlink ref="F8" r:id="rId7" tooltip="Activation of the MAPK pathway mediates resistance to PI3K ..." display="https://pubmed.ncbi.nlm.nih.gov/33684943/?utm_source=chatgpt.com" xr:uid="{FB27068F-62DC-4FE0-8447-2CD2BC1A8736}"/>
+    <hyperlink ref="F9" r:id="rId8" tooltip="Efficacy of PI3K inhibitors in advanced breast cancer - PMC" display="https://pmc.ncbi.nlm.nih.gov/articles/PMC6923787/?utm_source=chatgpt.com" xr:uid="{A40E43E7-68F8-4C72-AD29-7E287D5A2AAC}"/>
+    <hyperlink ref="F10" r:id="rId9" tooltip="_x000a_            Mechanisms of Resistance to PI3K Inhibitors in Cancer: Adaptive Responses, Drug Tolerance and Cellular Plasticity - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC8037590/" xr:uid="{AC1E63BD-CC17-45D1-9FA0-27F84BE8AAEB}"/>
+    <hyperlink ref="F11" r:id="rId10" tooltip="final overall survival results from SOLAR-1" display="https://pubmed.ncbi.nlm.nih.gov/33246021/?utm_source=chatgpt.com" xr:uid="{7C7297A9-4221-4D29-B05F-0CA799409A33}"/>
+    <hyperlink ref="F12" r:id="rId11" tooltip="_x000a_            A bi-steric mTORC1-selective inhibitor overcomes drug resistance in breast cancer - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC10328828/" xr:uid="{AAAEBF75-CB65-48F5-A971-2DAFCA9DD859}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B71A86D-30D2-4A83-BB96-ADD463C01457}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="32.90625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="10.6328125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6328125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="14.90625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="15.08984375" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H10" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" tooltip="_x000a_            The PI3K/AKT/mTOR and CDK4/6 Pathways in Endocrine Resistant HR+/HER2− Metastatic Breast Cancer: Biological Mechanisms and New Treatments - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC6770492/" xr:uid="{ADB069D7-A109-4752-A348-151A70C78700}"/>
+    <hyperlink ref="G3" r:id="rId2" tooltip="Deregulated E2F Activity as a Cancer-Cell Specific ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC9956157/?utm_source=chatgpt.com" xr:uid="{E9611637-B35C-46AA-822B-12FF2258FF67}"/>
+    <hyperlink ref="G4" r:id="rId3" tooltip="Investigation of ribociclib, abemaciclib and palbociclib ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC12325956/?utm_source=chatgpt.com" xr:uid="{FB3B6AE5-58B3-48DE-ACF3-4D87F92E0CC2}"/>
+    <hyperlink ref="G5" r:id="rId4" tooltip="_x000a_            The PI3K/AKT/mTOR and CDK4/6 Pathways in Endocrine Resistant HR+/HER2− Metastatic Breast Cancer: Biological Mechanisms and New Treatments - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC6770492/" xr:uid="{1993D015-19B1-4914-91ED-4153ECD2D2A3}"/>
+    <hyperlink ref="G6" r:id="rId5" tooltip="Aberrant FGFR signaling mediates resistance to CDK4/6 inhibitors in ER+ breast cancer - PubMed" display="https://pubmed.ncbi.nlm.nih.gov/30914635/" xr:uid="{936D2A3A-DDE4-44E2-94CA-866093B09551}"/>
+    <hyperlink ref="G7" r:id="rId6" tooltip="MAPK reliance via acquired CDK4/6 inhibitor resistance in ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC6125187/?utm_source=chatgpt.com" xr:uid="{9DD72F01-84D7-4038-A65B-DCE8F324B5FB}"/>
+    <hyperlink ref="G8" r:id="rId7" tooltip="c-myc regulates the sensitivity of breast cancer cells to palbociclib via c-myc/miR-29b-3p/CDK6 axis - PubMed" display="https://pubmed.ncbi.nlm.nih.gov/32934206/" xr:uid="{D1F296C0-4492-4C3E-9ECB-7CC63020DDC2}"/>
+    <hyperlink ref="G9" r:id="rId8" tooltip="Palbociclib Induces Senescence in Melanoma and Breast Cancer Cells and Leads to Additive Growth Arrest in Combination With Irradiation - PubMed" display="https://pubmed.ncbi.nlm.nih.gov/34722291/" xr:uid="{7F0EF830-076F-4D12-B16D-4AAE54AD3978}"/>
+    <hyperlink ref="G10" r:id="rId9" tooltip="_x000a_            Sustained mTORC1 activity during palbociclib-induced growth arrest triggers senescence in ER+ breast cancer cells - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC7849761/" xr:uid="{6CF0162A-48C6-4855-9C72-ED86B858634A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECA0B77E-D4CD-4224-A02D-1F102B600FD9}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="57.1796875" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="5" hidden="1" customWidth="1"/>
-    <col min="3" max="4" width="0" style="5" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" style="5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="121.26953125" style="5" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" style="5" customWidth="1"/>
+    <col min="3" max="4" width="8.7265625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="16.36328125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="121.26953125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1508,7 +4303,386 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2ACE8A6-A7DE-43CA-AE8F-3ED7E1B1513A}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42416EB7-F010-40E9-AB77-D8E433FCD901}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="76.6328125" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="21.81640625" customWidth="1"/>
+    <col min="4" max="4" width="33.6328125" customWidth="1"/>
+    <col min="5" max="5" width="76.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G3" r:id="rId1" tooltip="Mechanisms of sensitivity and resistance to CDK4/CDK6 ..." display="https://www.sciencedirect.com/science/article/pii/S136876462400061X?utm_source=chatgpt.com" xr:uid="{049EFEE6-979C-4B0F-9EE9-AF012EB0188E}"/>
+    <hyperlink ref="G4" r:id="rId2" tooltip="A narrative review of the clinical development of CDK4/6 ..." display="https://tbcr.amegroups.org/article/view/60627/html?utm_source=chatgpt.com" xr:uid="{0372E62D-B77D-40C8-868B-CB739B19C729}"/>
+    <hyperlink ref="G5" r:id="rId3" tooltip="Molecular mechanisms of resistance to CDK4/6 inhibitors in ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC6767051/?utm_source=chatgpt.com" xr:uid="{B33FCD46-49D9-4DD9-8AC1-4516ED673453}"/>
+    <hyperlink ref="G6" r:id="rId4" tooltip="Molecular mechanisms of resistance to CDK4/6 inhibitors in ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC6767051/?utm_source=chatgpt.com" xr:uid="{CBA29B8D-853E-48E9-BB60-B29E97B21E39}"/>
+    <hyperlink ref="G7" r:id="rId5" tooltip="Polyclonal RB1 mutations and acquired resistance to CDK ..." display="https://www.annalsofoncology.org/article/S0923-7534%2819%2935498-5/fulltext?utm_source=chatgpt.com" xr:uid="{84A26746-912F-4E8F-8A6A-9BA28711DEA7}"/>
+    <hyperlink ref="G8" r:id="rId6" tooltip="The PI3K/AKT/mTOR and CDK4/6 Pathways in Endocrine ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC6770492/?utm_source=chatgpt.com" xr:uid="{09D5B66E-F730-4273-BEE4-4B2A986AFC94}"/>
+    <hyperlink ref="G9" r:id="rId7" tooltip="Aberrant FGFR signaling mediates resistance to CDK4/6 ..." display="https://pubmed.ncbi.nlm.nih.gov/30914635/?utm_source=chatgpt.com" xr:uid="{46AAF4E6-9B7C-4315-89D9-4BD566D98769}"/>
+    <hyperlink ref="G10" r:id="rId8" tooltip="Recent advances of highly selective CDK4/6 inhibitors in ..." display="https://jhoonline.biomedcentral.com/articles/10.1186/s13045-017-0467-2?utm_source=chatgpt.com" xr:uid="{6C868405-3341-453F-897F-789256F6E6BE}"/>
+    <hyperlink ref="G11" r:id="rId9" tooltip="Article The CDK4/6 Inhibitor Abemaciclib Induces a T Cell ..." display="https://www.sciencedirect.com/science/article/pii/S2211124718302341?utm_source=chatgpt.com" xr:uid="{228967E7-72C1-4AEC-9D61-96591079003D}"/>
+    <hyperlink ref="G12" r:id="rId10" tooltip="CDK4/6 inhibitors induce breast cancer senescence with ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC10766199/?utm_source=chatgpt.com" xr:uid="{088F9682-C34D-4A80-B3D9-9029D8E6AF95}"/>
+    <hyperlink ref="G13" r:id="rId11" tooltip="Loss of the FAT1 tumor suppressor promotes resistance to ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC6294301/?utm_source=chatgpt.com" xr:uid="{C0D3B413-83C3-4CD2-952D-902F4E90BBC8}"/>
+    <hyperlink ref="G14" r:id="rId12" tooltip="Serum thymidine kinase 1 activity as a pharmacodynamic ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC5699111/?utm_source=chatgpt.com" xr:uid="{F344E931-35B7-4ADF-9485-2686E4A018D3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FA1EEF3-D42D-419E-B47C-813B1BE4F11F}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1791,7 +4965,1213 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD005598-F88A-42C9-82A3-ED18CC072B7D}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="43.08984375" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" customWidth="1"/>
+    <col min="3" max="3" width="20.7265625" customWidth="1"/>
+    <col min="4" max="4" width="59.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" tooltip="IFN-γ–related mRNA profile predicts clinical response to PD-1 ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC5531419/?utm_source=chatgpt.com" xr:uid="{B37E21C0-3842-4837-975A-22630EC5B398}"/>
+    <hyperlink ref="D3" r:id="rId2" tooltip="Immune-related Gene Expression Predicts Response to ..." display="https://aacrjournals.org/clincancerres/article/27/9/2584/672319/Immune-related-Gene-Expression-Predicts-Response?utm_source=chatgpt.com" xr:uid="{95540B0A-A251-4617-ADA0-85DEF33FA7BB}"/>
+    <hyperlink ref="D4" r:id="rId3" tooltip="Atezolizumab and Nab-Paclitaxel in Advanced Triple ..." display="https://www.nejm.org/doi/full/10.1056/NEJMoa1809615?utm_source=chatgpt.com" xr:uid="{9632AE93-D9E5-4436-A76E-2A21E057B128}"/>
+    <hyperlink ref="D5" r:id="rId4" tooltip="WNT/β-Catenin Signaling Pathway Regulating T Cell ..." display="https://www.frontiersin.org/journals/immunology/articles/10.3389/fimmu.2019.02293/full?utm_source=chatgpt.com" xr:uid="{48F825C2-1C30-4BA1-9105-C44AA85B5F98}"/>
+    <hyperlink ref="D6" r:id="rId5" tooltip="TGF-β attenuates tumour response to PD-L1 blockade by ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC6028240/?utm_source=chatgpt.com" xr:uid="{6D0C3DBE-D2B0-41A0-9171-AB034BDDA0FD}"/>
+    <hyperlink ref="D7" r:id="rId6" tooltip="Mutations Associated with Acquired Resistance to PD-1 ..." display="https://www.nejm.org/doi/full/10.1056/NEJMoa1604958?utm_source=chatgpt.com" xr:uid="{2ECC1E5F-BA9E-47C1-8888-65313C7D30DB}"/>
+    <hyperlink ref="D8" r:id="rId7" tooltip="PD-1 and LAG-3 dual blockade: emerging mechanisms ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC11667783/?utm_source=chatgpt.com" xr:uid="{E0B0E07F-C514-4AAC-A88A-B610CE77878F}"/>
+    <hyperlink ref="D9" r:id="rId8" tooltip="The PI3K/Akt/mTOR Signaling Pathway in Triple-Negative ..." display="https://www.mdpi.com/2072-6694/17/13/2232?utm_source=chatgpt.com" xr:uid="{6E1CF29B-2C6F-4658-9667-8CB0EC2F5BC6}"/>
+    <hyperlink ref="D10" r:id="rId9" tooltip="Hypoxia and the phenomenon of immune exclusion" display="https://translational-medicine.biomedcentral.com/articles/10.1186/s12967-020-02667-4?utm_source=chatgpt.com" xr:uid="{6F94DAA7-79D1-4698-81C8-658890CDD69A}"/>
+    <hyperlink ref="D11" r:id="rId10" tooltip="Homologous Recombination Repair Deficiency and the ..." display="https://pubmed.ncbi.nlm.nih.gov/31901781/?utm_source=chatgpt.com" xr:uid="{CC1D437E-AA18-4787-88C3-98705360EF0C}"/>
+    <hyperlink ref="D12" r:id="rId11" tooltip="CXCL9, CXCL10, CXCL11/CXCR3 axis for immune ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC5801162/?utm_source=chatgpt.com" xr:uid="{C5CAAC87-50D6-4E51-AED2-97C888807E70}"/>
+    <hyperlink ref="D13" r:id="rId12" tooltip="IDO expression in breast cancer: an assessment of 281 ..." display="https://www.sciencedirect.com/science/article/pii/S0893395222033026?utm_source=chatgpt.com" xr:uid="{443FD336-C056-4EE5-B406-D38E6591E052}"/>
+    <hyperlink ref="D14" r:id="rId13" tooltip="CD28 costimulation: from mechanism to therapy - PMC" display="https://pmc.ncbi.nlm.nih.gov/articles/PMC4932896/?utm_source=chatgpt.com" xr:uid="{BAC58AB0-2B32-4E11-A3A6-6033FC70C906}"/>
+    <hyperlink ref="D15" r:id="rId14" tooltip="Targeting Myeloid-Derived Suppressor Cell, a Promising ..." display="https://www.frontiersin.org/journals/immunology/articles/10.3389/fimmu.2020.00783/full?utm_source=chatgpt.com" xr:uid="{50CBD3CE-1BDB-4CBD-97C9-2ACD3DA8588F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0066A164-0B0F-4DE2-A1FF-1B702E3AE7BE}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="65.6328125" customWidth="1"/>
+    <col min="4" max="4" width="40.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="F14" s="10"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" tooltip="Resistance Mechanisms to Anti-angiogenic Therapies in ..." display="https://www.frontiersin.org/journals/oncology/articles/10.3389/fonc.2020.00221/full?utm_source=chatgpt.com" xr:uid="{5AE048DB-EC3A-4116-A29D-A21FAECB036D}"/>
+    <hyperlink ref="E10" r:id="rId2" tooltip="Bevacizumab improves tumor infiltration of mature dendritic ..." display="https://pubmed.ncbi.nlm.nih.gov/34188163/?utm_source=chatgpt.com" xr:uid="{FD6645BF-BA19-4C8C-AB66-AE04BA250040}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A689E78E-7E44-4C47-BD07-52120BC1A88F}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.54296875" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" customWidth="1"/>
+    <col min="3" max="3" width="62.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E25042D-B0C0-40CF-B8CA-9018F11CAEEC}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="58.6328125" customWidth="1"/>
+    <col min="2" max="2" width="45.6328125" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" customWidth="1"/>
+    <col min="4" max="4" width="78.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E12" r:id="rId1" tooltip="Resistance to PD-1/PD-L1 blockade cancer immunotherapy" display="https://biomarkerres.biomedcentral.com/articles/10.1186/s40364-020-00212-5?utm_source=chatgpt.com" xr:uid="{0D643552-AF06-490A-BB87-2AB9BE3BC418}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2E625D9-702D-4F69-BE1A-CA4853F3FA2C}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="37.1796875" customWidth="1"/>
+    <col min="2" max="2" width="19.1796875" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" customWidth="1"/>
+    <col min="4" max="4" width="67.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="116" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="116" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>466</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="116" x14ac:dyDescent="0.35">
+      <c r="A10" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>470</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="116" x14ac:dyDescent="0.35">
+      <c r="A11" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>474</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB792D0-0BB9-4D3C-A350-C002E67F0EB2}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2039,547 +6419,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B71A86D-30D2-4A83-BB96-ADD463C01457}">
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="32.90625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="10.6328125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6328125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6328125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="14.90625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="15.08984375" hidden="1" customWidth="1"/>
-    <col min="7" max="8" width="0" hidden="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="H10" s="2"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" tooltip="_x000a_            The PI3K/AKT/mTOR and CDK4/6 Pathways in Endocrine Resistant HR+/HER2− Metastatic Breast Cancer: Biological Mechanisms and New Treatments - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC6770492/" xr:uid="{ADB069D7-A109-4752-A348-151A70C78700}"/>
-    <hyperlink ref="G3" r:id="rId2" tooltip="Deregulated E2F Activity as a Cancer-Cell Specific ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC9956157/?utm_source=chatgpt.com" xr:uid="{E9611637-B35C-46AA-822B-12FF2258FF67}"/>
-    <hyperlink ref="G4" r:id="rId3" tooltip="Investigation of ribociclib, abemaciclib and palbociclib ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC12325956/?utm_source=chatgpt.com" xr:uid="{FB3B6AE5-58B3-48DE-ACF3-4D87F92E0CC2}"/>
-    <hyperlink ref="G5" r:id="rId4" tooltip="_x000a_            The PI3K/AKT/mTOR and CDK4/6 Pathways in Endocrine Resistant HR+/HER2− Metastatic Breast Cancer: Biological Mechanisms and New Treatments - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC6770492/" xr:uid="{1993D015-19B1-4914-91ED-4153ECD2D2A3}"/>
-    <hyperlink ref="G6" r:id="rId5" tooltip="Aberrant FGFR signaling mediates resistance to CDK4/6 inhibitors in ER+ breast cancer - PubMed" display="https://pubmed.ncbi.nlm.nih.gov/30914635/" xr:uid="{936D2A3A-DDE4-44E2-94CA-866093B09551}"/>
-    <hyperlink ref="G7" r:id="rId6" tooltip="MAPK reliance via acquired CDK4/6 inhibitor resistance in ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC6125187/?utm_source=chatgpt.com" xr:uid="{9DD72F01-84D7-4038-A65B-DCE8F324B5FB}"/>
-    <hyperlink ref="G8" r:id="rId7" tooltip="c-myc regulates the sensitivity of breast cancer cells to palbociclib via c-myc/miR-29b-3p/CDK6 axis - PubMed" display="https://pubmed.ncbi.nlm.nih.gov/32934206/" xr:uid="{D1F296C0-4492-4C3E-9ECB-7CC63020DDC2}"/>
-    <hyperlink ref="G9" r:id="rId8" tooltip="Palbociclib Induces Senescence in Melanoma and Breast Cancer Cells and Leads to Additive Growth Arrest in Combination With Irradiation - PubMed" display="https://pubmed.ncbi.nlm.nih.gov/34722291/" xr:uid="{7F0EF830-076F-4D12-B16D-4AAE54AD3978}"/>
-    <hyperlink ref="G10" r:id="rId9" tooltip="_x000a_            Sustained mTORC1 activity during palbociclib-induced growth arrest triggers senescence in ER+ breast cancer cells - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC7849761/" xr:uid="{6CF0162A-48C6-4855-9C72-ED86B858634A}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBA3F18-2088-485A-86C4-2ECCC7AACBA1}">
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="57.08984375" customWidth="1"/>
-    <col min="2" max="2" width="36.81640625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="34.6328125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="38.36328125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="30.6328125" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="0" hidden="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" tooltip="Alpelisib for PIK3CA-Mutated, Hormone Receptor-Positive ..." display="https://pubmed.ncbi.nlm.nih.gov/31091374/?utm_source=chatgpt.com" xr:uid="{A6441139-4B5A-443B-912E-E9F8FFD4519C}"/>
-    <hyperlink ref="F3" r:id="rId2" tooltip="_x000a_            Mechanisms of Resistance to PI3K Inhibitors in Cancer: Adaptive Responses, Drug Tolerance and Cellular Plasticity - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC8037590/" xr:uid="{90CAEBC1-18BD-4AA1-92EB-7CF1A821D599}"/>
-    <hyperlink ref="F4" r:id="rId3" tooltip="A Phase I Study of Alpelisib in Combination with Trastuzumab ..." display="https://pubmed.ncbi.nlm.nih.gov/33947692/?utm_source=chatgpt.com" xr:uid="{861CB97A-7260-4140-BD4B-DDD71A9EB749}"/>
-    <hyperlink ref="F5" r:id="rId4" tooltip="Alpelisib for PIK3CA-Mutated, Hormone Receptor-Positive ..." display="https://pubmed.ncbi.nlm.nih.gov/31091374/?utm_source=chatgpt.com" xr:uid="{8A37E234-813C-41FD-AF57-B758FFB3FAD3}"/>
-    <hyperlink ref="F6" r:id="rId5" tooltip="PIK3CA mutation-driven immune signature as a prognostic ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC10927816/?utm_source=chatgpt.com" xr:uid="{5B9E55B5-AC01-4784-BFC7-833FF9D8BB6E}"/>
-    <hyperlink ref="F7" r:id="rId6" tooltip="Metabolic Imaging Detects Resistance to PI3Kα Inhibition ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC7562820/?utm_source=chatgpt.com" xr:uid="{F708B21A-B654-4FDC-B4E4-F67DF785A925}"/>
-    <hyperlink ref="F8" r:id="rId7" tooltip="Activation of the MAPK pathway mediates resistance to PI3K ..." display="https://pubmed.ncbi.nlm.nih.gov/33684943/?utm_source=chatgpt.com" xr:uid="{FB27068F-62DC-4FE0-8447-2CD2BC1A8736}"/>
-    <hyperlink ref="F9" r:id="rId8" tooltip="Efficacy of PI3K inhibitors in advanced breast cancer - PMC" display="https://pmc.ncbi.nlm.nih.gov/articles/PMC6923787/?utm_source=chatgpt.com" xr:uid="{A40E43E7-68F8-4C72-AD29-7E287D5A2AAC}"/>
-    <hyperlink ref="F10" r:id="rId9" tooltip="_x000a_            Mechanisms of Resistance to PI3K Inhibitors in Cancer: Adaptive Responses, Drug Tolerance and Cellular Plasticity - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC8037590/" xr:uid="{AC1E63BD-CC17-45D1-9FA0-27F84BE8AAEB}"/>
-    <hyperlink ref="F11" r:id="rId10" tooltip="final overall survival results from SOLAR-1" display="https://pubmed.ncbi.nlm.nih.gov/33246021/?utm_source=chatgpt.com" xr:uid="{7C7297A9-4221-4D29-B05F-0CA799409A33}"/>
-    <hyperlink ref="F12" r:id="rId11" tooltip="_x000a_            A bi-steric mTORC1-selective inhibitor overcomes drug resistance in breast cancer - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC10328828/" xr:uid="{AAAEBF75-CB65-48F5-A971-2DAFCA9DD859}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/singscore_new_code/results/Deep_search_results/deepsearch_2_CORRECTED_data_prompt1_results_pathway_name_curated.csv.xlsx
+++ b/singscore_new_code/results/Deep_search_results/deepsearch_2_CORRECTED_data_prompt1_results_pathway_name_curated.csv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GS\PySingscore_replicate\singscore_new_code\results\Deep_search_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67375948-A760-4A4D-A18D-1330DF3CC4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10F65B4-F40D-45F9-8D5D-BD064F3107BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="25" activeTab="25" xr2:uid="{2CB371E1-5584-44EB-81C2-385450FA2A4A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2CB371E1-5584-44EB-81C2-385450FA2A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Abemaciclib_corrected" sheetId="6" r:id="rId1"/>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="1364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="1346">
   <si>
     <t>Pathway</t>
   </si>
@@ -142,12 +142,6 @@
     <t>HALLMARK_G2M_CHECKPOINT</t>
   </si>
   <si>
-    <t>Rationale (corrected, concise)</t>
-  </si>
-  <si>
-    <t>Ref(s) (PubMed/PMCID)</t>
-  </si>
-  <si>
     <t>Incorrect</t>
   </si>
   <si>
@@ -229,90 +223,45 @@
     <t>Partially Sensitive (context-dependent)  (ESR1 mutations often cause endocrine resistance; alpelisib + fulvestrant can still have activity) ESR1 activating mutations drive endocrine resistance but combining PI3Kα inhibition with ER downregulation (fulvestrant) can have activity in some settings; evidence is mixed and depends on prior therapies (CDK4/6 exposure etc.). ESR1 mutation is not a simple “positive” predictor but combination therapy may work in some ESR1-mutant cases. (PubMed Central)</t>
   </si>
   <si>
-    <t>Original regulation (you gave)</t>
-  </si>
-  <si>
-    <t>Judgement (orig)</t>
-  </si>
-  <si>
-    <t>Rationale (concise, mechanistic)</t>
-  </si>
-  <si>
     <t>Reference(s) / PMID</t>
   </si>
   <si>
-    <t>↓ (suppressed)</t>
-  </si>
-  <si>
     <t>Aromatase inhibitors (anastrozole) reduce peripheral estrogen → less ERα activation → loss of ER transcriptional program (estrogen response signatures fall) → growth suppression in ER+ tumours.</t>
   </si>
   <si>
     <t>Review on endocrine therapy mechanism/resistance. (PubMed Central)</t>
   </si>
   <si>
-    <t>↓ (inhibited)</t>
-  </si>
-  <si>
     <t>Anastrozole directly inhibits aromatase (CYP19A1), reducing conversion of androgens→estrogens → decreased steroid biosynthesis flux and tumour estrogen supply.</t>
   </si>
   <si>
     <t>Mechanistic/clinical AI data. (PubMed Central)</t>
   </si>
   <si>
-    <t>↑ (upregulated in resistance)</t>
-  </si>
-  <si>
     <t>PI3K/AKT/mTOR activation provides ER-independent proliferative/survival signalling and is a common escape mechanism from estrogen deprivation; PI3K pathway activation correlates with AI resistance and combining PI3K/mTOR inhibitors can re-sensitize.</t>
   </si>
   <si>
     <t>Reviews &amp; experimental work. (PubMed Central) (see PMID 23553037).</t>
   </si>
   <si>
-    <t>↑ (up in resistance)</t>
-  </si>
-  <si>
     <t>Upregulation or activation of RTKs (EGFR/HER2) stimulates downstream PI3K/MAPK signalling, bypassing ER blockade to support proliferation → associated with endocrine resistance.</t>
   </si>
   <si>
     <t>Reviews on RTK bypass in endocrine resistance. (ScienceDirect)</t>
   </si>
   <si>
-    <t>Correct (contextual)</t>
-  </si>
-  <si>
     <t>MAPK (RAS→RAF→MEK→ERK) downstream of RTKs can drive cell-cycle and survival independent of ER; MAPK activation is observed in AI-resistant models and mediates growth despite estrogen deprivation.</t>
   </si>
   <si>
     <t>RTK–MAPK cross-talk literature and AI resistance reviews. (PubMed Central)</t>
   </si>
   <si>
-    <t>↑ (upregulated)</t>
-  </si>
-  <si>
-    <t>Correct (specific to anastrozole)</t>
-  </si>
-  <si>
     <t>Anastrozole has been shown to increase FASN protein (via decreased ubiquitin-mediated degradation) in resistant models; high FASN correlates with worse outcome on anastrozole and can support growth/metabolic rewiring.</t>
   </si>
   <si>
     <t>Experimental study (FASN / anastrozole) — PMID 34667110. (PubMed)</t>
   </si>
   <si>
-    <r>
-      <t>Incorrect</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (your “sensitive” interpretation is not supported generally)</t>
-    </r>
-  </si>
-  <si>
     <t>Several studies show interferon-stimulated genes (ISGs) are constitutively upregulated in AI-resistant models (e.g., IFITM1, PLSCR1); in some contexts suppression of chronic ISG signalling can re-sensitize cells to estradiol-induced apoptosis. So IFN/ISG ↑ is associated with resistance biology in many reports — the relationship with immune activation is complex and context dependent.</t>
   </si>
   <si>
@@ -331,12 +280,6 @@
     <t>ER–NFκB crosstalk reviews. (PubMed Central)</t>
   </si>
   <si>
-    <t>↓ (downregulated)</t>
-  </si>
-  <si>
-    <t>Partly correct / contextual</t>
-  </si>
-  <si>
     <t>Effective estrogen suppression causes G1 arrest (↓Cyclin D/CDK4/6 activity) → reduced E2F activity and S-phase gene expression (E2F targets fall). However, **E2F ↑ is a marker of</t>
   </si>
   <si>
@@ -909,21 +852,6 @@
   </si>
   <si>
     <r>
-      <t>Upregulation is primarily post-treatment/adaptive</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (CDK4/6i-induced PD-L1 on tumor and immune cells)</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>Acquired/adaptive resistance</t>
     </r>
     <r>
@@ -1145,9 +1073,6 @@
       </rPr>
       <t xml:space="preserve"> (intrinsic or acquired)</t>
     </r>
-  </si>
-  <si>
-    <t>REACTOME_ABERRANT_REGULATION_OF_MITOTIC_G_S_TRANSITION_IN_CANCER_DUE_TO_RB1_DEFECTS</t>
   </si>
   <si>
     <t>KEGG_MEDICUS_REFERENCE_P16_CELL_CYCLE_G1_S</t>
@@ -10260,9 +10185,6 @@
   </si>
   <si>
     <t>Tokunaga E et al. Breast Cancer 2006 (Akt activation linked to resistance to endocrine therapy and chemotherapy). PMID:16755107</t>
-  </si>
-  <si>
-    <t>KEGG_CYTOKINE_CYTOKINE_RECEPTOR_INTERACTION (incl. IL6/IL8)</t>
   </si>
   <si>
     <t>Pro-tumor cytokine loops (e.g., IL6/IL8) can create NF-κB/Wnt–reinforced autocrine feedback, enriching drug-tolerant/CSC-like populations after chemotherapy exposure/withdrawal, supporting resistance.</t>
@@ -10362,7 +10284,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10442,6 +10364,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -10464,7 +10392,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10534,6 +10462,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -11027,8 +10956,8 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="76.6328125" customWidth="1"/>
-    <col min="2" max="2" width="19" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="21.81640625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="22.26953125" customWidth="1"/>
     <col min="4" max="4" width="33.6328125" customWidth="1"/>
     <col min="5" max="5" width="76.26953125" customWidth="1"/>
     <col min="6" max="6" width="41.1796875" customWidth="1"/>
@@ -11036,30 +10965,30 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
-        <v>1329</v>
+        <v>1312</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>3</v>
@@ -11068,21 +10997,21 @@
         <v>4</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>1326</v>
+        <v>1309</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>1327</v>
+        <v>1310</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>1328</v>
+        <v>1311</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -11091,21 +11020,21 @@
         <v>4</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -11114,21 +11043,21 @@
         <v>4</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -11137,21 +11066,21 @@
         <v>4</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
@@ -11160,21 +11089,21 @@
         <v>5</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>204</v>
+        <v>1262</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>6</v>
@@ -11183,21 +11112,21 @@
         <v>5</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>3</v>
@@ -11206,21 +11135,21 @@
         <v>5</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>3</v>
@@ -11229,21 +11158,21 @@
         <v>5</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>3</v>
@@ -11252,21 +11181,21 @@
         <v>5</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>6</v>
@@ -11275,44 +11204,44 @@
         <v>4</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>184</v>
+        <v>6</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1330</v>
+        <v>1313</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
-        <v>1334</v>
+        <v>1317</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>1331</v>
+        <v>1314</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>1332</v>
+        <v>1315</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>1333</v>
+        <v>1316</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>6</v>
@@ -11321,16 +11250,16 @@
         <v>5</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -11344,22 +11273,22 @@
         <v>4</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:A14" xr:uid="{42416EB7-F010-40E9-AB77-D8E433FCD901}">
     <filterColumn colId="0">
-      <colorFilter dxfId="1" cellColor="0"/>
+      <colorFilter dxfId="0" cellColor="0"/>
     </filterColumn>
   </autoFilter>
   <hyperlinks>
@@ -11394,24 +11323,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>471</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>3</v>
@@ -11420,15 +11349,15 @@
         <v>4</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>472</v>
+        <v>455</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>473</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>3</v>
@@ -11437,66 +11366,66 @@
         <v>4</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>475</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>479</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>3</v>
@@ -11505,27 +11434,27 @@
         <v>5</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>487</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="58" x14ac:dyDescent="0.35">
@@ -11533,50 +11462,50 @@
         <v>12</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="18" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -11614,24 +11543,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>595</v>
+        <v>578</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>3</v>
@@ -11640,32 +11569,32 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>524</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>3</v>
@@ -11674,32 +11603,32 @@
         <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>598</v>
+        <v>581</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>512</v>
+        <v>495</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>3</v>
@@ -11708,15 +11637,15 @@
         <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>3</v>
@@ -11725,44 +11654,44 @@
         <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -11770,21 +11699,21 @@
         <v>8</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1336</v>
+        <v>1319</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1337</v>
+        <v>1320</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>3</v>
@@ -11793,15 +11722,15 @@
         <v>5</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>3</v>
@@ -11810,10 +11739,10 @@
         <v>5</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -11858,18 +11787,18 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>3</v>
@@ -11878,18 +11807,18 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>3</v>
@@ -11898,18 +11827,18 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>3</v>
@@ -11918,18 +11847,18 @@
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>3</v>
@@ -11938,18 +11867,18 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>3</v>
@@ -11958,18 +11887,18 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>6</v>
@@ -11978,18 +11907,18 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>3</v>
@@ -11998,18 +11927,18 @@
         <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>6</v>
@@ -12018,18 +11947,18 @@
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>3</v>
@@ -12038,18 +11967,18 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>3</v>
@@ -12058,13 +11987,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -12098,259 +12027,259 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="B1" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="C1" t="s">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="D1" t="s">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="E1" t="s">
-        <v>536</v>
+        <v>519</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="D2" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="E2" t="s">
-        <v>579</v>
+        <v>562</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="D3" t="s">
-        <v>541</v>
+        <v>524</v>
       </c>
       <c r="E3" t="s">
-        <v>580</v>
+        <v>563</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>543</v>
+        <v>526</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>581</v>
+        <v>564</v>
       </c>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>545</v>
+        <v>528</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="D5" t="s">
-        <v>547</v>
+        <v>530</v>
       </c>
       <c r="E5" t="s">
-        <v>582</v>
+        <v>565</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="D6" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="E6" t="s">
-        <v>583</v>
+        <v>566</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
-        <v>600</v>
+        <v>583</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="D7" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="E7" t="s">
-        <v>584</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
-        <v>601</v>
+        <v>584</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="D8" t="s">
-        <v>556</v>
+        <v>539</v>
       </c>
       <c r="E8" t="s">
-        <v>585</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>557</v>
+        <v>540</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="D9" t="s">
-        <v>559</v>
+        <v>542</v>
       </c>
       <c r="E9" t="s">
-        <v>586</v>
+        <v>569</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="21" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="D10" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="E10" t="s">
-        <v>587</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="21" t="s">
-        <v>602</v>
+        <v>585</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>563</v>
+        <v>546</v>
       </c>
       <c r="D11" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="E11" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A12" s="21" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>565</v>
+        <v>548</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="D12" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
       <c r="E12" t="s">
-        <v>589</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="21" t="s">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="D13" t="s">
-        <v>570</v>
+        <v>553</v>
       </c>
       <c r="E13" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>571</v>
+        <v>554</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>572</v>
+        <v>555</v>
       </c>
       <c r="D14" t="s">
-        <v>573</v>
+        <v>556</v>
       </c>
       <c r="E14" t="s">
-        <v>591</v>
+        <v>574</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
       <c r="C15" s="21" t="s">
+        <v>541</v>
+      </c>
+      <c r="D15" t="s">
         <v>558</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>575</v>
-      </c>
-      <c r="E15" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -12358,16 +12287,16 @@
         <v>8</v>
       </c>
       <c r="B16" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>560</v>
+      </c>
+      <c r="D16" t="s">
+        <v>561</v>
+      </c>
+      <c r="E16" t="s">
         <v>576</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>577</v>
-      </c>
-      <c r="D16" t="s">
-        <v>578</v>
-      </c>
-      <c r="E16" t="s">
-        <v>593</v>
       </c>
     </row>
   </sheetData>
@@ -12394,87 +12323,87 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C1" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="D1" t="s">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="E1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>608</v>
+        <v>591</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="E2" t="s">
-        <v>611</v>
+        <v>594</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>615</v>
+        <v>598</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" s="21" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>617</v>
+        <v>600</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="E4" t="s">
-        <v>619</v>
+        <v>602</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>617</v>
+        <v>600</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>621</v>
+        <v>604</v>
       </c>
       <c r="E5" t="s">
-        <v>622</v>
+        <v>605</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -12482,51 +12411,51 @@
         <v>8</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>623</v>
+        <v>606</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>625</v>
+        <v>608</v>
       </c>
       <c r="E6" t="s">
-        <v>626</v>
+        <v>609</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>657</v>
+        <v>640</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>627</v>
+        <v>610</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>629</v>
+        <v>612</v>
       </c>
       <c r="F7" s="10"/>
     </row>
     <row r="8" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>631</v>
+        <v>614</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
@@ -12534,19 +12463,19 @@
     </row>
     <row r="9" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>634</v>
+        <v>617</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>636</v>
+        <v>619</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>637</v>
+        <v>620</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
@@ -12554,54 +12483,54 @@
     </row>
     <row r="10" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>639</v>
+        <v>622</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>641</v>
+        <v>624</v>
       </c>
       <c r="F10" s="10"/>
     </row>
     <row r="11" spans="1:8" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>645</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>656</v>
+        <v>639</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>648</v>
+        <v>631</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>649</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>
@@ -12627,104 +12556,104 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>659</v>
+        <v>642</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>660</v>
+        <v>643</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>661</v>
+        <v>644</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>662</v>
+        <v>645</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>706</v>
+        <v>689</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>663</v>
+        <v>646</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>666</v>
+        <v>649</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>707</v>
+        <v>690</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>668</v>
+        <v>651</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>669</v>
+        <v>652</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>670</v>
+        <v>653</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>672</v>
+        <v>655</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>673</v>
+        <v>656</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>674</v>
+        <v>657</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>675</v>
+        <v>658</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>676</v>
+        <v>659</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>677</v>
+        <v>660</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
@@ -12732,84 +12661,84 @@
         <v>8</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>678</v>
+        <v>661</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>679</v>
+        <v>662</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>680</v>
+        <v>663</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
-        <v>708</v>
+        <v>691</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>682</v>
+        <v>665</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
-        <v>709</v>
+        <v>692</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>686</v>
+        <v>669</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
-        <v>710</v>
+        <v>693</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>687</v>
+        <v>670</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>689</v>
+        <v>672</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>690</v>
+        <v>673</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
-        <v>711</v>
+        <v>694</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>691</v>
+        <v>674</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>692</v>
+        <v>675</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>693</v>
+        <v>676</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="58" x14ac:dyDescent="0.35">
@@ -12817,33 +12746,33 @@
         <v>12</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>694</v>
+        <v>677</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>695</v>
+        <v>678</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>696</v>
+        <v>679</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>697</v>
+        <v>680</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>698</v>
+        <v>681</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>699</v>
+        <v>682</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>700</v>
+        <v>683</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>701</v>
+        <v>684</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="58" x14ac:dyDescent="0.35">
@@ -12851,16 +12780,16 @@
         <v>9</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>702</v>
+        <v>685</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>703</v>
+        <v>686</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>704</v>
+        <v>687</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>705</v>
+        <v>688</v>
       </c>
     </row>
   </sheetData>
@@ -12910,140 +12839,140 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>712</v>
+        <v>695</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>713</v>
+        <v>696</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>714</v>
+        <v>697</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>746</v>
+        <v>729</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>715</v>
+        <v>698</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>716</v>
+        <v>699</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>717</v>
+        <v>700</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>747</v>
+        <v>730</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>718</v>
+        <v>701</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>719</v>
+        <v>702</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>720</v>
+        <v>703</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>721</v>
+        <v>704</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>722</v>
+        <v>705</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>723</v>
+        <v>706</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>725</v>
+        <v>708</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>751</v>
+        <v>734</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>726</v>
+        <v>709</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>727</v>
+        <v>710</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>728</v>
+        <v>711</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
-        <v>753</v>
+        <v>736</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>729</v>
+        <v>712</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>752</v>
+        <v>735</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>730</v>
+        <v>713</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>745</v>
+        <v>728</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>731</v>
+        <v>714</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>732</v>
+        <v>715</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>733</v>
+        <v>716</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -13051,51 +12980,51 @@
         <v>9</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>735</v>
+        <v>718</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>736</v>
+        <v>719</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>737</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
-        <v>744</v>
+        <v>727</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>738</v>
+        <v>721</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>739</v>
+        <v>722</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>743</v>
+        <v>726</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>740</v>
+        <v>723</v>
       </c>
       <c r="F10" s="10"/>
     </row>
     <row r="11" spans="1:7" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19" t="s">
-        <v>750</v>
+        <v>733</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>741</v>
+        <v>724</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>749</v>
+        <v>732</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>742</v>
+        <v>725</v>
       </c>
     </row>
   </sheetData>
@@ -13125,24 +13054,24 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>754</v>
+        <v>737</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>755</v>
+        <v>738</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>3</v>
@@ -13151,15 +13080,15 @@
         <v>4</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>756</v>
+        <v>739</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>757</v>
+        <v>740</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>785</v>
+        <v>768</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>3</v>
@@ -13168,34 +13097,34 @@
         <v>5</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>758</v>
+        <v>741</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>759</v>
+        <v>742</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
-        <v>787</v>
+        <v>770</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>760</v>
+        <v>743</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>786</v>
+        <v>769</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>761</v>
+        <v>744</v>
       </c>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>3</v>
@@ -13204,32 +13133,32 @@
         <v>5</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>763</v>
+        <v>746</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>764</v>
+        <v>747</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>765</v>
+        <v>748</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>766</v>
+        <v>749</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>767</v>
+        <v>750</v>
       </c>
     </row>
     <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
-        <v>788</v>
+        <v>771</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>3</v>
@@ -13238,44 +13167,44 @@
         <v>5</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>768</v>
+        <v>751</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>769</v>
+        <v>752</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>770</v>
+        <v>753</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>771</v>
+        <v>754</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>772</v>
+        <v>755</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
-        <v>789</v>
+        <v>772</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>773</v>
+        <v>756</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>774</v>
+        <v>757</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>775</v>
+        <v>758</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -13289,32 +13218,32 @@
         <v>4</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>776</v>
+        <v>759</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>777</v>
+        <v>760</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19" t="s">
-        <v>790</v>
+        <v>773</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>778</v>
+        <v>761</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>779</v>
+        <v>762</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>780</v>
+        <v>763</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
-        <v>792</v>
+        <v>775</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>3</v>
@@ -13323,27 +13252,27 @@
         <v>5</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>781</v>
+        <v>764</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>782</v>
+        <v>765</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>791</v>
+        <v>774</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>783</v>
+        <v>766</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>784</v>
+        <v>767</v>
       </c>
     </row>
   </sheetData>
@@ -13375,7 +13304,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4CD495A-E26B-43A9-9E9F-C9ED6109B088}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="45.81640625" customWidth="1"/>
@@ -13386,173 +13315,173 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>793</v>
+        <v>776</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>845</v>
+        <v>828</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>794</v>
+        <v>777</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>795</v>
+        <v>778</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="18" t="s">
-        <v>844</v>
+        <v>827</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>842</v>
+        <v>825</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>843</v>
+        <v>826</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>797</v>
+        <v>780</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>798</v>
+        <v>781</v>
       </c>
       <c r="F3" s="10"/>
     </row>
     <row r="4" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>799</v>
+        <v>782</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>802</v>
+        <v>785</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>803</v>
+        <v>786</v>
       </c>
     </row>
     <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="18" t="s">
-        <v>846</v>
+        <v>829</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>804</v>
+        <v>787</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>805</v>
+        <v>788</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>806</v>
+        <v>789</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>807</v>
+        <v>790</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>808</v>
+        <v>791</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>809</v>
+        <v>792</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>810</v>
+        <v>793</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>847</v>
+        <v>830</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>811</v>
+        <v>794</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>812</v>
+        <v>795</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>814</v>
+        <v>797</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>815</v>
+        <v>798</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>816</v>
+        <v>799</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>817</v>
+        <v>800</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>818</v>
+        <v>801</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>851</v>
+        <v>834</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>819</v>
+        <v>802</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>820</v>
+        <v>803</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>821</v>
+        <v>804</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="18" t="s">
-        <v>850</v>
+        <v>833</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>849</v>
+        <v>832</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>808</v>
+        <v>791</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="29" x14ac:dyDescent="0.35">
@@ -13560,102 +13489,107 @@
         <v>8</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>824</v>
+        <v>807</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>825</v>
+        <v>808</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>826</v>
+        <v>809</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>852</v>
+        <v>835</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>827</v>
+        <v>810</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>828</v>
+        <v>811</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>829</v>
+        <v>812</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>830</v>
+        <v>813</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>853</v>
+        <v>836</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>831</v>
+        <v>814</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>832</v>
+        <v>815</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>833</v>
+        <v>816</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="18" t="s">
-        <v>848</v>
+        <v>831</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>834</v>
+        <v>817</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>835</v>
+        <v>818</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>803</v>
+        <v>786</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="18" t="s">
-        <v>856</v>
+        <v>839</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>855</v>
+        <v>838</v>
       </c>
       <c r="C15" s="19" t="s">
         <v>5</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>836</v>
+        <v>819</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>837</v>
+        <v>820</v>
       </c>
       <c r="F15" s="10"/>
     </row>
     <row r="16" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>854</v>
+        <v>837</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>838</v>
+        <v>821</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>839</v>
+        <v>822</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>840</v>
+        <v>823</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>841</v>
+        <v>824</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="25" t="s">
+        <v>828</v>
       </c>
     </row>
   </sheetData>
@@ -13701,19 +13635,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="24" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="F1"/>
     </row>
@@ -13728,10 +13662,10 @@
         <v>4</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1338</v>
+        <v>1321</v>
       </c>
       <c r="E2" t="s">
-        <v>1339</v>
+        <v>1322</v>
       </c>
       <c r="F2"/>
     </row>
@@ -13746,10 +13680,10 @@
         <v>4</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1340</v>
+        <v>1323</v>
       </c>
       <c r="E3" t="s">
-        <v>1339</v>
+        <v>1322</v>
       </c>
       <c r="F3"/>
     </row>
@@ -13761,13 +13695,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1341</v>
+        <v>1324</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1342</v>
+        <v>1325</v>
       </c>
       <c r="E4" t="s">
-        <v>1343</v>
+        <v>1326</v>
       </c>
       <c r="F4"/>
     </row>
@@ -13779,13 +13713,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1344</v>
+        <v>1327</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1345</v>
+        <v>1328</v>
       </c>
       <c r="E5" t="s">
-        <v>1346</v>
+        <v>1329</v>
       </c>
       <c r="F5"/>
     </row>
@@ -13800,10 +13734,10 @@
         <v>5</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1347</v>
+        <v>1330</v>
       </c>
       <c r="E6" t="s">
-        <v>1348</v>
+        <v>1331</v>
       </c>
       <c r="F6"/>
     </row>
@@ -13818,16 +13752,16 @@
         <v>5</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1349</v>
+        <v>1332</v>
       </c>
       <c r="E7" t="s">
-        <v>1350</v>
+        <v>1333</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>1351</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>3</v>
@@ -13836,10 +13770,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="E8" t="s">
-        <v>1353</v>
+        <v>1335</v>
       </c>
       <c r="F8"/>
     </row>
@@ -13854,10 +13788,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1354</v>
+        <v>1336</v>
       </c>
       <c r="E9" t="s">
-        <v>1355</v>
+        <v>1337</v>
       </c>
       <c r="F9"/>
     </row>
@@ -13872,10 +13806,10 @@
         <v>4</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1356</v>
+        <v>1338</v>
       </c>
       <c r="E10" t="s">
-        <v>1339</v>
+        <v>1322</v>
       </c>
       <c r="F10"/>
     </row>
@@ -13890,10 +13824,10 @@
         <v>5</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1357</v>
+        <v>1339</v>
       </c>
       <c r="E11" t="s">
-        <v>1358</v>
+        <v>1340</v>
       </c>
       <c r="F11"/>
     </row>
@@ -13917,24 +13851,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>136</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>3</v>
@@ -13943,15 +13877,15 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
@@ -13960,15 +13894,15 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
@@ -13977,15 +13911,15 @@
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>3</v>
@@ -13994,15 +13928,15 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="23" t="s">
-        <v>1325</v>
+        <v>1308</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>3</v>
@@ -14011,15 +13945,15 @@
         <v>5</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>3</v>
@@ -14028,15 +13962,15 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>3</v>
@@ -14045,15 +13979,15 @@
         <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
-        <v>1324</v>
+        <v>1307</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>6</v>
@@ -14062,10 +13996,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -14079,32 +14013,32 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>3</v>
@@ -14113,10 +14047,10 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -14167,19 +14101,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -14193,22 +14127,22 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
@@ -14223,10 +14157,10 @@
         <v>4</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="H3" s="2"/>
     </row>
@@ -14247,16 +14181,16 @@
         <v>5</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>3</v>
@@ -14271,16 +14205,16 @@
         <v>5</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>3</v>
@@ -14295,16 +14229,16 @@
         <v>5</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>3</v>
@@ -14319,16 +14253,16 @@
         <v>5</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>3</v>
@@ -14343,16 +14277,16 @@
         <v>5</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>3</v>
@@ -14367,22 +14301,22 @@
         <v>4</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>3</v>
@@ -14391,10 +14325,10 @@
         <v>5</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="H10" s="2"/>
     </row>
@@ -14426,24 +14360,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C1" t="s">
-        <v>1041</v>
+        <v>1024</v>
       </c>
       <c r="D1" t="s">
-        <v>1042</v>
+        <v>1025</v>
       </c>
       <c r="E1" t="s">
-        <v>1043</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>3</v>
@@ -14452,15 +14386,15 @@
         <v>4</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>1044</v>
+        <v>1027</v>
       </c>
       <c r="E2" t="s">
-        <v>1045</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>3</v>
@@ -14469,15 +14403,15 @@
         <v>4</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>1046</v>
+        <v>1029</v>
       </c>
       <c r="E3" t="s">
-        <v>1047</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="21" t="s">
-        <v>1269</v>
+        <v>1252</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>3</v>
@@ -14486,15 +14420,15 @@
         <v>4</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>1048</v>
+        <v>1031</v>
       </c>
       <c r="E4" t="s">
-        <v>1049</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
-        <v>1270</v>
+        <v>1253</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>3</v>
@@ -14503,15 +14437,15 @@
         <v>4</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>1050</v>
+        <v>1033</v>
       </c>
       <c r="E5" t="s">
-        <v>1051</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>3</v>
@@ -14520,10 +14454,10 @@
         <v>4</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>1052</v>
+        <v>1035</v>
       </c>
       <c r="E6" t="s">
-        <v>1053</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="58" x14ac:dyDescent="0.35">
@@ -14537,15 +14471,15 @@
         <v>4</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>1054</v>
+        <v>1037</v>
       </c>
       <c r="E7" t="s">
-        <v>1055</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B8" s="21" t="s">
         <v>3</v>
@@ -14554,15 +14488,15 @@
         <v>5</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>1056</v>
+        <v>1039</v>
       </c>
       <c r="E8" t="s">
-        <v>1057</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B9" s="21" t="s">
         <v>3</v>
@@ -14571,15 +14505,15 @@
         <v>4</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>1058</v>
+        <v>1041</v>
       </c>
       <c r="E9" t="s">
-        <v>1059</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A10" s="21" t="s">
-        <v>1271</v>
+        <v>1254</v>
       </c>
       <c r="B10" s="21" t="s">
         <v>3</v>
@@ -14588,10 +14522,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>1060</v>
+        <v>1043</v>
       </c>
       <c r="E10" t="s">
-        <v>1061</v>
+        <v>1044</v>
       </c>
     </row>
   </sheetData>
@@ -14612,87 +14546,87 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1012</v>
+        <v>995</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>1011</v>
+        <v>994</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1013</v>
+        <v>996</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>1014</v>
+        <v>997</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1015</v>
+        <v>998</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1016</v>
+        <v>999</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1017</v>
+        <v>1000</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>1018</v>
+        <v>1001</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1019</v>
+        <v>1002</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1020</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1021</v>
+        <v>1004</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>1022</v>
+        <v>1005</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1023</v>
+        <v>1006</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1024</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1025</v>
+        <v>1008</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1026</v>
+        <v>1009</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1027</v>
+        <v>1010</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1028</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
@@ -14700,50 +14634,50 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>1029</v>
+        <v>1012</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1030</v>
+        <v>1013</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1031</v>
+        <v>1014</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1032</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>1272</v>
+        <v>1255</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1033</v>
+        <v>1016</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>1034</v>
+        <v>1017</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1035</v>
+        <v>1018</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1036</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>1265</v>
+        <v>1248</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>1037</v>
+        <v>1020</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1038</v>
+        <v>1021</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1039</v>
+        <v>1022</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1040</v>
+        <v>1023</v>
       </c>
     </row>
   </sheetData>
@@ -14765,53 +14699,53 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1062</v>
+        <v>1045</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>1277</v>
+        <v>1260</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>1063</v>
+        <v>1046</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1064</v>
+        <v>1047</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>1065</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>1063</v>
+        <v>1046</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1066</v>
+        <v>1049</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1067</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -14822,132 +14756,132 @@
         <v>3</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>1063</v>
+        <v>1046</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1068</v>
+        <v>1051</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1069</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="18" t="s">
-        <v>1275</v>
+        <v>1258</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1070</v>
+        <v>1053</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>1071</v>
+        <v>1054</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>1072</v>
+        <v>1055</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>1274</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
-        <v>1276</v>
+        <v>1259</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>1070</v>
+        <v>1053</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>1071</v>
+        <v>1054</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>1073</v>
+        <v>1056</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>1074</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>1075</v>
+        <v>1058</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1076</v>
+        <v>1059</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1077</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>1078</v>
+        <v>1061</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1075</v>
+        <v>1058</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1079</v>
+        <v>1062</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1080</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>1273</v>
+        <v>1256</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1081</v>
+        <v>1064</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1075</v>
+        <v>1058</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1082</v>
+        <v>1065</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1083</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>1278</v>
+        <v>1261</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1084</v>
+        <v>1067</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1085</v>
+        <v>1068</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1086</v>
+        <v>1069</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1087</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>1279</v>
+        <v>1262</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1088</v>
+        <v>1071</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1075</v>
+        <v>1058</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1089</v>
+        <v>1072</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1090</v>
+        <v>1073</v>
       </c>
     </row>
   </sheetData>
@@ -14986,87 +14920,87 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
-        <v>872</v>
+        <v>855</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>857</v>
+        <v>840</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>858</v>
+        <v>841</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>859</v>
+        <v>842</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>860</v>
+        <v>843</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>876</v>
+        <v>859</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>861</v>
+        <v>844</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>862</v>
+        <v>845</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>863</v>
+        <v>846</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>864</v>
+        <v>847</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
-        <v>873</v>
+        <v>856</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>865</v>
+        <v>848</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>866</v>
+        <v>849</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>867</v>
+        <v>850</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>868</v>
+        <v>851</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
-        <v>875</v>
+        <v>858</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>869</v>
+        <v>852</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>870</v>
+        <v>853</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>874</v>
+        <v>857</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>871</v>
+        <v>854</v>
       </c>
     </row>
   </sheetData>
@@ -15092,105 +15026,105 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>877</v>
+        <v>860</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>878</v>
+        <v>861</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>879</v>
+        <v>862</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>880</v>
+        <v>863</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>881</v>
+        <v>864</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>909</v>
+        <v>892</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>882</v>
+        <v>865</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>910</v>
+        <v>893</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>883</v>
+        <v>866</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>884</v>
+        <v>867</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
-        <v>908</v>
+        <v>891</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>907</v>
+        <v>890</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>885</v>
+        <v>868</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>886</v>
+        <v>869</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>887</v>
+        <v>870</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
-        <v>906</v>
+        <v>889</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>904</v>
+        <v>887</v>
       </c>
       <c r="C5" s="19" t="s">
+        <v>871</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>905</v>
-      </c>
       <c r="E5" s="13" t="s">
-        <v>889</v>
+        <v>872</v>
       </c>
       <c r="F5" s="10"/>
     </row>
     <row r="6" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>890</v>
+        <v>873</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>891</v>
+        <v>874</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>892</v>
+        <v>875</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>893</v>
+        <v>876</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
@@ -15198,50 +15132,50 @@
         <v>16</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>894</v>
+        <v>877</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>895</v>
+        <v>878</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>896</v>
+        <v>879</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>897</v>
+        <v>880</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
-        <v>915</v>
+        <v>898</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>898</v>
+        <v>881</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>899</v>
+        <v>882</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>900</v>
+        <v>883</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>901</v>
+        <v>884</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
-        <v>914</v>
+        <v>897</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>912</v>
+        <v>895</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>902</v>
+        <v>885</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>913</v>
+        <v>896</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>903</v>
+        <v>886</v>
       </c>
     </row>
   </sheetData>
@@ -15267,36 +15201,36 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
-        <v>931</v>
+        <v>914</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>916</v>
+        <v>899</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>917</v>
+        <v>900</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>918</v>
+        <v>901</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
@@ -15304,67 +15238,67 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>934</v>
+        <v>917</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>919</v>
+        <v>902</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>920</v>
+        <v>903</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>933</v>
+        <v>916</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
-        <v>932</v>
+        <v>915</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>921</v>
+        <v>904</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>922</v>
+        <v>905</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>923</v>
+        <v>906</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
-        <v>851</v>
+        <v>834</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>924</v>
+        <v>907</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>925</v>
+        <v>908</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>926</v>
+        <v>909</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>927</v>
+        <v>910</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>930</v>
+        <v>913</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>928</v>
+        <v>911</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>929</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -15392,24 +15326,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>935</v>
+        <v>918</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>3</v>
@@ -15418,15 +15352,15 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>936</v>
+        <v>919</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>937</v>
+        <v>920</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>954</v>
+        <v>937</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>3</v>
@@ -15435,13 +15369,13 @@
         <v>4</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>938</v>
+        <v>921</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>3</v>
@@ -15450,22 +15384,22 @@
         <v>5</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>939</v>
+        <v>922</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>955</v>
+        <v>938</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>940</v>
+        <v>923</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>941</v>
+        <v>924</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -15477,16 +15411,16 @@
         <v>3</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>942</v>
+        <v>925</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>943</v>
+        <v>926</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>3</v>
@@ -15495,13 +15429,13 @@
         <v>5</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>944</v>
+        <v>927</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>3</v>
@@ -15510,13 +15444,13 @@
         <v>5</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>945</v>
+        <v>928</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>3</v>
@@ -15525,13 +15459,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>946</v>
+        <v>929</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>956</v>
+        <v>939</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>3</v>
@@ -15540,13 +15474,13 @@
         <v>5</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>947</v>
+        <v>930</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>3</v>
@@ -15555,13 +15489,13 @@
         <v>5</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>948</v>
+        <v>931</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>3</v>
@@ -15570,13 +15504,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>949</v>
+        <v>932</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>3</v>
@@ -15585,13 +15519,13 @@
         <v>5</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>950</v>
+        <v>933</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>957</v>
+        <v>940</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>6</v>
@@ -15600,22 +15534,22 @@
         <v>5</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>951</v>
+        <v>934</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>958</v>
+        <v>941</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>952</v>
+        <v>935</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>953</v>
+        <v>936</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -15654,138 +15588,138 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>959</v>
+        <v>942</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>994</v>
+        <v>977</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>1002</v>
+        <v>985</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>960</v>
+        <v>943</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>961</v>
+        <v>944</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>995</v>
+        <v>978</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>962</v>
+        <v>945</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>963</v>
+        <v>946</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>964</v>
+        <v>947</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>997</v>
+        <v>980</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>996</v>
+        <v>979</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>1001</v>
+        <v>984</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>965</v>
+        <v>948</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>966</v>
+        <v>949</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="18" t="s">
-        <v>993</v>
+        <v>976</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>992</v>
+        <v>975</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>967</v>
+        <v>950</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>968</v>
+        <v>951</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>969</v>
+        <v>952</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="116" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
-        <v>1363</v>
+        <v>1345</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>1361</v>
+        <v>1343</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>1362</v>
+        <v>1344</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>970</v>
+        <v>953</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>971</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="145" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>972</v>
+        <v>955</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>998</v>
+        <v>981</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>973</v>
+        <v>956</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>974</v>
+        <v>957</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="18" t="s">
-        <v>1000</v>
+        <v>983</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>999</v>
+        <v>982</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>998</v>
+        <v>981</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>975</v>
+        <v>958</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>976</v>
+        <v>959</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
@@ -15793,33 +15727,33 @@
         <v>16</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1006</v>
+        <v>989</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>977</v>
+        <v>960</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>978</v>
+        <v>961</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1005</v>
+        <v>988</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1003</v>
+        <v>986</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>980</v>
+        <v>963</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="58" x14ac:dyDescent="0.35">
@@ -15827,74 +15761,74 @@
         <v>8</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1007</v>
+        <v>990</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1008</v>
+        <v>991</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>981</v>
+        <v>964</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>982</v>
+        <v>965</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>1009</v>
+        <v>992</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>1010</v>
+        <v>993</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>983</v>
+        <v>966</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>984</v>
+        <v>967</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="18" t="s">
-        <v>1360</v>
+        <v>1342</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>1359</v>
+        <v>1341</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>998</v>
+        <v>981</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>985</v>
+        <v>968</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>986</v>
+        <v>969</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="18" t="s">
-        <v>991</v>
+        <v>974</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>987</v>
+        <v>970</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>988</v>
+        <v>971</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>989</v>
+        <v>972</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>990</v>
+        <v>973</v>
       </c>
       <c r="F14" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:A14" xr:uid="{87C87E3C-5F1A-43BC-9910-4CE25E2C972D}">
     <filterColumn colId="0">
-      <colorFilter dxfId="0" cellColor="0"/>
+      <colorFilter dxfId="4" cellColor="0"/>
     </filterColumn>
   </autoFilter>
   <hyperlinks>
@@ -15928,87 +15862,87 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1091</v>
+        <v>1074</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1092</v>
+        <v>1075</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1093</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>1011</v>
+        <v>994</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1280</v>
+        <v>1263</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>1289</v>
+        <v>1272</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1094</v>
+        <v>1077</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1095</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1281</v>
+        <v>1264</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>1290</v>
+        <v>1273</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1096</v>
+        <v>1079</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1097</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1282</v>
+        <v>1265</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>1291</v>
+        <v>1274</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1098</v>
+        <v>1081</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1099</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1292</v>
+        <v>1275</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1293</v>
+        <v>1276</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1100</v>
+        <v>1083</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1101</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
@@ -16016,50 +15950,50 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>1283</v>
+        <v>1266</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1294</v>
+        <v>1277</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1102</v>
+        <v>1085</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>1103</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="87" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>1272</v>
+        <v>1255</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1284</v>
+        <v>1267</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>1295</v>
+        <v>1278</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1104</v>
+        <v>1087</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1105</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>751</v>
+        <v>734</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>1285</v>
+        <v>1268</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1106</v>
+        <v>1089</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1107</v>
+        <v>1090</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1108</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="58" x14ac:dyDescent="0.35">
@@ -16067,67 +16001,67 @@
         <v>12</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1286</v>
+        <v>1269</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1296</v>
+        <v>1279</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1109</v>
+        <v>1092</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1110</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>1297</v>
+        <v>1280</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1287</v>
+        <v>1270</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1298</v>
+        <v>1281</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1111</v>
+        <v>1094</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1112</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1288</v>
+        <v>1271</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1113</v>
+        <v>1096</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1114</v>
+        <v>1097</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1115</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>1299</v>
+        <v>1282</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>1300</v>
+        <v>1283</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1116</v>
+        <v>1099</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1117</v>
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
@@ -16161,44 +16095,36 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FA1EEF3-D42D-419E-B47C-813B1BE4F11F}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36.36328125" style="5" customWidth="1"/>
     <col min="2" max="2" width="11.36328125" style="5" customWidth="1"/>
     <col min="3" max="3" width="8.90625" style="5" customWidth="1"/>
     <col min="4" max="4" width="162.81640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="24.7265625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="27.81640625" style="5" customWidth="1"/>
-    <col min="7" max="8" width="8.7265625" style="5" customWidth="1"/>
+    <col min="5" max="6" width="8.7265625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>48</v>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
@@ -16207,21 +16133,15 @@
         <v>4</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>3</v>
@@ -16230,21 +16150,15 @@
         <v>4</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>3</v>
@@ -16253,21 +16167,15 @@
         <v>5</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>3</v>
@@ -16276,21 +16184,15 @@
         <v>5</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>3</v>
@@ -16299,21 +16201,15 @@
         <v>5</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>3</v>
@@ -16322,19 +16218,13 @@
         <v>5</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
@@ -16345,21 +16235,15 @@
         <v>5</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>3</v>
@@ -16368,21 +16252,15 @@
         <v>5</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>3</v>
@@ -16391,21 +16269,15 @@
         <v>5</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>6</v>
@@ -16414,29 +16286,23 @@
         <v>4</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" t="s">
-        <v>79</v>
+        <v>63</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" tooltip="Endocrine therapy resistance in breast cancer" display="https://pmc.ncbi.nlm.nih.gov/articles/PMC5558537/?utm_source=chatgpt.com" xr:uid="{00438247-1907-4BB4-9DA8-3233DA8AAB8B}"/>
-    <hyperlink ref="G3" r:id="rId2" tooltip="Endocrine therapy resistance in breast cancer" display="https://pmc.ncbi.nlm.nih.gov/articles/PMC5558537/?utm_source=chatgpt.com" xr:uid="{E292DE4C-75DC-4CE0-A417-030D7C6C9650}"/>
-    <hyperlink ref="G4" r:id="rId3" tooltip="Role of PI3K/Akt/mTOR pathway in mediating endocrine ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC9400772/?utm_source=chatgpt.com" xr:uid="{314F16C2-FF1B-4997-9F41-8A6412166128}"/>
-    <hyperlink ref="G5" r:id="rId4" tooltip="Overcoming Endocrine Resistance in Breast Cancer" display="https://www.sciencedirect.com/science/article/pii/S1535610820301495?utm_source=chatgpt.com" xr:uid="{9D54BB7B-E33C-4371-8346-D4058A2F6E0E}"/>
-    <hyperlink ref="G6" r:id="rId5" tooltip="_x000a_            The interaction between ER and NFκB in resistance to endocrine therapy - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC3680926/" xr:uid="{346EB317-776E-44CF-B378-1D09AFF0F9C9}"/>
-    <hyperlink ref="G7" r:id="rId6" tooltip="Anastrozole Regulates Fatty Acid Synthase in Breast Cancer - PubMed" display="https://pubmed.ncbi.nlm.nih.gov/34667110/" xr:uid="{B4D54B31-B86E-492A-940A-4EC378EE3DE6}"/>
-    <hyperlink ref="G8" r:id="rId7" tooltip="Targeting interferon response genes sensitizes aromatase ..." display="https://pubmed.ncbi.nlm.nih.gov/25588716/?utm_source=chatgpt.com" xr:uid="{A088BFF2-461E-4B38-B77D-964154CE97A1}"/>
-    <hyperlink ref="G9" r:id="rId8" tooltip="Article IL6/STAT3 Signaling Hijacks Estrogen Receptor α ..." display="https://www.sciencedirect.com/science/article/pii/S1535610820303111?utm_source=chatgpt.com" xr:uid="{DC3120E1-13DE-4002-8355-34243EE8BE14}"/>
-    <hyperlink ref="G10" r:id="rId9" tooltip="_x000a_            The interaction between ER and NFκB in resistance to endocrine therapy - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC3680926/" xr:uid="{E0754C57-0248-4628-A3E6-865053B6BEDA}"/>
+    <hyperlink ref="E2" r:id="rId1" tooltip="Endocrine therapy resistance in breast cancer" display="https://pmc.ncbi.nlm.nih.gov/articles/PMC5558537/?utm_source=chatgpt.com" xr:uid="{00438247-1907-4BB4-9DA8-3233DA8AAB8B}"/>
+    <hyperlink ref="E3" r:id="rId2" tooltip="Endocrine therapy resistance in breast cancer" display="https://pmc.ncbi.nlm.nih.gov/articles/PMC5558537/?utm_source=chatgpt.com" xr:uid="{E292DE4C-75DC-4CE0-A417-030D7C6C9650}"/>
+    <hyperlink ref="E4" r:id="rId3" tooltip="Role of PI3K/Akt/mTOR pathway in mediating endocrine ..." display="https://pmc.ncbi.nlm.nih.gov/articles/PMC9400772/?utm_source=chatgpt.com" xr:uid="{314F16C2-FF1B-4997-9F41-8A6412166128}"/>
+    <hyperlink ref="E5" r:id="rId4" tooltip="Overcoming Endocrine Resistance in Breast Cancer" display="https://www.sciencedirect.com/science/article/pii/S1535610820301495?utm_source=chatgpt.com" xr:uid="{9D54BB7B-E33C-4371-8346-D4058A2F6E0E}"/>
+    <hyperlink ref="E6" r:id="rId5" tooltip="_x000a_            The interaction between ER and NFκB in resistance to endocrine therapy - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC3680926/" xr:uid="{346EB317-776E-44CF-B378-1D09AFF0F9C9}"/>
+    <hyperlink ref="E7" r:id="rId6" tooltip="Anastrozole Regulates Fatty Acid Synthase in Breast Cancer - PubMed" display="https://pubmed.ncbi.nlm.nih.gov/34667110/" xr:uid="{B4D54B31-B86E-492A-940A-4EC378EE3DE6}"/>
+    <hyperlink ref="E8" r:id="rId7" tooltip="Targeting interferon response genes sensitizes aromatase ..." display="https://pubmed.ncbi.nlm.nih.gov/25588716/?utm_source=chatgpt.com" xr:uid="{A088BFF2-461E-4B38-B77D-964154CE97A1}"/>
+    <hyperlink ref="E9" r:id="rId8" tooltip="Article IL6/STAT3 Signaling Hijacks Estrogen Receptor α ..." display="https://www.sciencedirect.com/science/article/pii/S1535610820303111?utm_source=chatgpt.com" xr:uid="{DC3120E1-13DE-4002-8355-34243EE8BE14}"/>
+    <hyperlink ref="E10" r:id="rId9" tooltip="_x000a_            The interaction between ER and NFκB in resistance to endocrine therapy - PMC_x000a_        " display="https://pmc.ncbi.nlm.nih.gov/articles/PMC3680926/" xr:uid="{E0754C57-0248-4628-A3E6-865053B6BEDA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16456,87 +16322,87 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1217</v>
+        <v>1200</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1218</v>
+        <v>1201</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1219</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
-        <v>1304</v>
+        <v>1287</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1302</v>
+        <v>1285</v>
       </c>
       <c r="C2" s="19" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>1303</v>
+        <v>1286</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>1220</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>1011</v>
+        <v>994</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1221</v>
+        <v>1204</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1222</v>
+        <v>1205</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1223</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
-        <v>1224</v>
+        <v>1207</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>1309</v>
+        <v>1292</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1225</v>
+        <v>1208</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>1226</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
-        <v>1310</v>
+        <v>1293</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1227</v>
+        <v>1210</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1228</v>
+        <v>1211</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1229</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -16544,69 +16410,69 @@
         <v>16</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>1230</v>
+        <v>1213</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1231</v>
+        <v>1214</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>1232</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
-        <v>745</v>
+        <v>728</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1233</v>
+        <v>1216</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1234</v>
+        <v>1217</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1235</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
-        <v>1308</v>
+        <v>1291</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>1236</v>
+        <v>1219</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1307</v>
+        <v>1290</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>1237</v>
+        <v>1220</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
-        <v>1311</v>
+        <v>1294</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1238</v>
+        <v>1221</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1239</v>
+        <v>1222</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1240</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -16614,74 +16480,74 @@
         <v>9</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1241</v>
+        <v>1224</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1242</v>
+        <v>1225</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1243</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
-        <v>1312</v>
+        <v>1295</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1244</v>
+        <v>1227</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1245</v>
+        <v>1228</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1246</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>1247</v>
+        <v>1230</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1248</v>
+        <v>1231</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1249</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
-        <v>1314</v>
+        <v>1297</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>1313</v>
+        <v>1296</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>1250</v>
+        <v>1233</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>1251</v>
+        <v>1234</v>
       </c>
       <c r="F13" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:A13" xr:uid="{9700E5C8-2BFC-4436-B3BC-73E4DF7E1568}">
     <filterColumn colId="0">
-      <colorFilter dxfId="4" cellColor="0"/>
+      <colorFilter dxfId="3" cellColor="0"/>
     </filterColumn>
   </autoFilter>
   <hyperlinks>
@@ -16715,24 +16581,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1154</v>
+        <v>1137</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1155</v>
+        <v>1138</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1156</v>
+        <v>1139</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1157</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>1011</v>
+        <v>994</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>3</v>
@@ -16741,15 +16607,15 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1158</v>
+        <v>1141</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1159</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>1265</v>
+        <v>1248</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
@@ -16758,78 +16624,78 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1160</v>
+        <v>1143</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1161</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1162</v>
+        <v>1145</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1163</v>
+        <v>1146</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1164</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>1260</v>
+        <v>1243</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1165</v>
+        <v>1148</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1166</v>
+        <v>1149</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>1167</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>1259</v>
+        <v>1242</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1162</v>
+        <v>1145</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>1168</v>
+        <v>1151</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>1169</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1170</v>
+        <v>1153</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1171</v>
+        <v>1154</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1172</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -16837,33 +16703,33 @@
         <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1173</v>
+        <v>1156</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1174</v>
+        <v>1157</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1175</v>
+        <v>1158</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1176</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1177</v>
+        <v>1160</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1178</v>
+        <v>1161</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1179</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -16871,16 +16737,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1180</v>
+        <v>1163</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1263</v>
+        <v>1246</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1181</v>
+        <v>1164</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>1182</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -16894,61 +16760,61 @@
         <v>4</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1183</v>
+        <v>1166</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1184</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>1267</v>
+        <v>1250</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1185</v>
+        <v>1168</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1186</v>
+        <v>1169</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1187</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>1268</v>
+        <v>1251</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1188</v>
+        <v>1171</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1189</v>
+        <v>1172</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>1190</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>1264</v>
+        <v>1247</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1191</v>
+        <v>1174</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>5</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>1192</v>
+        <v>1175</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>1193</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -16962,136 +16828,136 @@
         <v>5</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1194</v>
+        <v>1177</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>1195</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>1254</v>
+        <v>1237</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>1253</v>
+        <v>1236</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1196</v>
+        <v>1179</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>1197</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>1266</v>
+        <v>1249</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1198</v>
+        <v>1181</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1199</v>
+        <v>1182</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1200</v>
+        <v>1183</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>1201</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>1262</v>
+        <v>1245</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1202</v>
+        <v>1185</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>1261</v>
+        <v>1244</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>1203</v>
+        <v>1186</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>1204</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>1258</v>
+        <v>1241</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1205</v>
+        <v>1188</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1206</v>
+        <v>1189</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>1207</v>
+        <v>1190</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>1208</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>1257</v>
+        <v>1240</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1205</v>
+        <v>1188</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>1206</v>
+        <v>1189</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>1209</v>
+        <v>1192</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>1210</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>1256</v>
+        <v>1239</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1211</v>
+        <v>1194</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1206</v>
+        <v>1189</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>1212</v>
+        <v>1195</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>1213</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>1255</v>
+        <v>1238</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1214</v>
+        <v>1197</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>1215</v>
+        <v>1198</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>1252</v>
+        <v>1235</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>1216</v>
+        <v>1199</v>
       </c>
       <c r="F22" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:A22" xr:uid="{E04435B0-AA60-45B4-AAF2-A4A9A0ED11D7}">
     <filterColumn colId="0">
-      <colorFilter dxfId="3" cellColor="0"/>
+      <colorFilter dxfId="2" cellColor="0"/>
     </filterColumn>
   </autoFilter>
   <hyperlinks>
@@ -17135,126 +17001,126 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
-        <v>1011</v>
+        <v>994</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1118</v>
+        <v>1101</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1119</v>
+        <v>1102</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1120</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1121</v>
+        <v>1104</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>1301</v>
+        <v>1284</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1122</v>
+        <v>1105</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1123</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1124</v>
+        <v>1107</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>1322</v>
+        <v>1305</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1125</v>
+        <v>1108</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1126</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
-        <v>1321</v>
+        <v>1304</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1127</v>
+        <v>1110</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1128</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
-        <v>1297</v>
+        <v>1280</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1129</v>
+        <v>1112</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1130</v>
+        <v>1113</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>1131</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>1132</v>
+        <v>1115</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1133</v>
+        <v>1116</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1134</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>3</v>
@@ -17263,118 +17129,118 @@
         <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1135</v>
+        <v>1118</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1136</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1137</v>
+        <v>1120</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1138</v>
+        <v>1121</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1139</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
-        <v>1306</v>
+        <v>1289</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>1140</v>
+        <v>1123</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>1141</v>
+        <v>1124</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>1305</v>
+        <v>1288</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>1142</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1143</v>
+        <v>1126</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1323</v>
+        <v>1306</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1144</v>
+        <v>1127</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1145</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
-        <v>1269</v>
+        <v>1252</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>1146</v>
+        <v>1129</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>1147</v>
+        <v>1130</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1148</v>
+        <v>1131</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1149</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
-        <v>1317</v>
+        <v>1300</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>1315</v>
+        <v>1298</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>1150</v>
+        <v>1133</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>1316</v>
+        <v>1299</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>1151</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="19" t="s">
-        <v>1320</v>
+        <v>1303</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>1318</v>
+        <v>1301</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>1152</v>
+        <v>1135</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>1319</v>
+        <v>1302</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>1153</v>
+        <v>1136</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:A14" xr:uid="{C10B296E-9153-482A-9851-5606BB7631C9}">
     <filterColumn colId="0">
-      <colorFilter dxfId="2" cellColor="0"/>
+      <colorFilter dxfId="1" cellColor="0"/>
     </filterColumn>
   </autoFilter>
   <hyperlinks>
@@ -17409,19 +17275,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -17435,15 +17301,15 @@
         <v>4</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -17452,32 +17318,32 @@
         <v>4</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -17486,15 +17352,15 @@
         <v>5</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
@@ -17503,15 +17369,15 @@
         <v>5</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>6</v>
@@ -17520,15 +17386,15 @@
         <v>5</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>3</v>
@@ -17537,15 +17403,15 @@
         <v>5</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>3</v>
@@ -17554,15 +17420,15 @@
         <v>5</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>3</v>
@@ -17571,49 +17437,49 @@
         <v>5</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
-        <v>1335</v>
+        <v>1318</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>3</v>
@@ -17622,15 +17488,15 @@
         <v>5</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>6</v>
@@ -17639,15 +17505,15 @@
         <v>5</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>3</v>
@@ -17656,10 +17522,10 @@
         <v>5</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -17700,75 +17566,75 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>3</v>
@@ -17777,32 +17643,32 @@
         <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>3</v>
@@ -17811,15 +17677,15 @@
         <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>3</v>
@@ -17828,15 +17694,15 @@
         <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>3</v>
@@ -17845,10 +17711,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -17856,21 +17722,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>3</v>
@@ -17879,10 +17745,10 @@
         <v>5</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -17890,50 +17756,50 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>5</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="F14" s="10"/>
     </row>
@@ -17965,138 +17831,138 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -18104,67 +17970,67 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -18190,53 +18056,53 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -18244,169 +18110,169 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -18430,24 +18296,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>3</v>
@@ -18456,15 +18322,15 @@
         <v>4</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>3</v>
@@ -18473,61 +18339,61 @@
         <v>4</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="87" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="116" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
@@ -18535,21 +18401,21 @@
         <v>16</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="116" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>3</v>
@@ -18558,44 +18424,44 @@
         <v>5</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="116" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="116" x14ac:dyDescent="0.35">
@@ -18603,16 +18469,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -18634,138 +18500,138 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>461</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="18" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="18" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="58" x14ac:dyDescent="0.35">
@@ -18773,85 +18639,85 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="18" t="s">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="F11" s="10"/>
     </row>
     <row r="12" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="18" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>654</v>
+        <v>637</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
